--- a/Templates/PEATREST_input_scenario_modelling - Copy.xlsx
+++ b/Templates/PEATREST_input_scenario_modelling - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://forestresearch-my.sharepoint.com/personal/jacob_osullivan_forestresearch_gov_uk/Documents/Turbines and trees/PEATREST/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="109_{2692C0AF-F37D-4242-A816-1D703B957833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F82AAEEE-F521-4E15-8AB5-6FABADC66858}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="109_{2692C0AF-F37D-4242-A816-1D703B957833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F02DA665-9944-4038-8445-8A201E19F8B3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forestry input data" sheetId="28" r:id="rId1"/>
@@ -319,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="166">
   <si>
     <t>Years after felling when replanting occurs</t>
   </si>
@@ -448,122 +448,7 @@
     <t>AREA 5</t>
   </si>
   <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> kg</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> C</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>kg C MJ</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>day</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>kg C m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-2</t>
-    </r>
-  </si>
-  <si>
     <t>Years when replanted forestry will be grown on wind farm site</t>
-  </si>
-  <si>
-    <r>
-      <t>MJ m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> yr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-1</t>
-    </r>
   </si>
   <si>
     <t>Average annual photosynthetically active radiation</t>
@@ -1087,100 +972,6 @@
   </si>
   <si>
     <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Worrall et al. (2009) Sci. Tot. Env</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dawson et al. (1995) J. Environ. Qual.,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dawson et al. (2002) J Hydrol</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Buckingham et al. (2008) Sci. Tot. Env.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Hope et al. (1997) J Hydrol.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Worrall et al., 2009, Dawson et al., 1995,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dawson et al., 2002, Buckingham et al., 2008, Hope et al., 1997</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Reprentative total aquatic carbon flux restored peatland (t CO</t>
     </r>
     <r>
@@ -1464,9 +1255,6 @@
     <t>a4</t>
   </si>
   <si>
-    <t>fE</t>
-  </si>
-  <si>
     <t>YC</t>
   </si>
   <si>
@@ -1476,22 +1264,122 @@
     <t>NPP_max_LCA</t>
   </si>
   <si>
-    <t>Example conversion</t>
-  </si>
-  <si>
-    <t>fE_LCA</t>
-  </si>
-  <si>
     <t>spp</t>
   </si>
   <si>
-    <t>SP</t>
+    <r>
+      <t>MJ m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> yr</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
   </si>
   <si>
-    <t>Not used</t>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> kg</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> C</t>
+    </r>
   </si>
   <si>
-    <t>SS</t>
+    <r>
+      <t>kg C MJ</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>day</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>kg C m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-2</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1503,7 +1391,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1542,12 +1430,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1574,12 +1456,6 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1616,11 +1492,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -2088,7 +1959,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2099,7 +1970,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2115,7 +1986,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2135,7 +2006,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2155,7 +2026,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2175,7 +2046,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2195,7 +2066,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2205,10 +2076,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2226,10 +2097,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2250,7 +2121,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2259,7 +2130,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2271,7 +2142,7 @@
     <xf numFmtId="49" fontId="5" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2289,25 +2160,25 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2319,7 +2190,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2337,19 +2208,19 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2367,13 +2238,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2391,13 +2262,13 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2474,16 +2345,16 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2498,16 +2369,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2519,28 +2390,28 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2549,13 +2420,13 @@
     <xf numFmtId="49" fontId="5" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2564,13 +2435,13 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="8" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2625,7 +2496,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2698,7 +2569,7 @@
     <xf numFmtId="49" fontId="5" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2767,7 +2638,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2782,13 +2653,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2816,54 +2683,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2874,7 +2698,7 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2885,6 +2709,123 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2921,89 +2862,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3128,10 +2986,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$Y$46:$Y$104</c:f>
+              <c:f>'Forestry input data'!$Y$46:$Y$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3165,112 +3023,112 @@
                 <c:pt idx="10">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="11">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="12">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="13">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="14">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="15">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="16">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="17">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="18">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="19">
                   <c:v>21</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="20">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="21">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="22">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="23">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="24">
                   <c:v>26</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="25">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="26">
                   <c:v>28</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="27">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="28">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="29">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="30">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="31">
                   <c:v>33</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="32">
                   <c:v>34</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="33">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="34">
                   <c:v>36</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="35">
                   <c:v>37</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="36">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="37">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="38">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="39">
                   <c:v>41</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="40">
                   <c:v>42</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="41">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="42">
                   <c:v>44</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="43">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="44">
                   <c:v>47</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="45">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="46">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -3278,150 +3136,150 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$Z$46:$Z$104</c:f>
+              <c:f>'Forestry input data'!$Z$46:$Z$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.7989160644090236E-2</c:v>
+                  <c:v>0.1290364100439193</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16823622889732903</c:v>
+                  <c:v>0.24142242497081623</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.24142242497081623</c:v>
+                  <c:v>0.339306551992404</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.30816902908106347</c:v>
+                  <c:v>0.42456006266284307</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.36904265551980675</c:v>
+                  <c:v>0.49881276637272765</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.42456006266284307</c:v>
+                  <c:v>0.56348416775983401</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.47519253975022735</c:v>
+                  <c:v>0.61981060367943874</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.56348416775983401</c:v>
+                  <c:v>0.71159684968733927</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.63692194522989865</c:v>
+                  <c:v>0.78122383760504466</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.66886887851740884</c:v>
+                  <c:v>0.80945392820367523</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.83404130925624387</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.85545602292540723</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.87410745882058327</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.89035218038568142</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.90450074139785641</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.91682362288973285</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.92755640399250094</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.69800482795979835</c:v>
+                  <c:v>0.9369042655519807</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.72457712966618337</c:v>
+                  <c:v>0.94504591261423754</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.74881135684904199</c:v>
+                  <c:v>0.95213699076773617</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.77091323472322271</c:v>
+                  <c:v>0.95831306165296648</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.79107038691459608</c:v>
+                  <c:v>0.96369219452298982</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.80945392820367523</c:v>
+                  <c:v>0.96837722339831622</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.82621991712506238</c:v>
+                  <c:v>0.97245771296661832</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.97601167080980511</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.84151068075388857</c:v>
+                  <c:v>0.97910703869145954</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85545602292540723</c:v>
+                  <c:v>0.98180299141390015</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.8681743261443593</c:v>
+                  <c:v>0.98415106807538888</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.87977355653825873</c:v>
+                  <c:v>0.98619615735397115</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.98797735565382583</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.89035218038568142</c:v>
+                  <c:v>0.98952871451949098</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9</c:v>
+                  <c:v>0.99087989160644085</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.90879891606440899</c:v>
+                  <c:v>0.99205671765275716</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.91682362288973285</c:v>
+                  <c:v>0.99308169029081061</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.92414224249708166</c:v>
+                  <c:v>0.99397440413925642</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.93081690290810637</c:v>
+                  <c:v>0.99475192539750223</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.99542911810385126</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.9369042655519807</c:v>
+                  <c:v>0.99601892829446503</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.94245600626628434</c:v>
+                  <c:v>0.99653263149547466</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.94751925397502268</c:v>
+                  <c:v>0.99698004827959796</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.99736973200810464</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.95213699076773617</c:v>
+                  <c:v>0.99770913234723224</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.95634841677598337</c:v>
+                  <c:v>0.99800473768503117</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.96018928294465022</c:v>
+                  <c:v>0.99848643875156384</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.96369219452298982</c:v>
+                  <c:v>0.99885184637850311</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.96688688785174093</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.96980048279597986</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.97245771296661832</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.9748811356849042</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.9770913234723223</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.97910703869145954</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.98094539282036752</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.98262199171250619</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.98415106807538888</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.98681743261443589</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.9890352180385682</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.99</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3459,10 +3317,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$Y$46:$Y$104</c:f>
+              <c:f>'Forestry input data'!$Y$46:$Y$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3496,112 +3354,112 @@
                 <c:pt idx="10">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="11">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="12">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="13">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="14">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="15">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="16">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="17">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="18">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="19">
                   <c:v>21</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="20">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="21">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="22">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="23">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="24">
                   <c:v>26</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="25">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="26">
                   <c:v>28</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="27">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="28">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="29">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="30">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="31">
                   <c:v>33</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="32">
                   <c:v>34</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="33">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="34">
                   <c:v>36</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="35">
                   <c:v>37</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="36">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="37">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="38">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="39">
                   <c:v>41</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="40">
                   <c:v>42</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="41">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="42">
                   <c:v>44</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="43">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="44">
                   <c:v>47</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="45">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="46">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -3609,150 +3467,150 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$AA$46:$AA$104</c:f>
+              <c:f>'Forestry input data'!$AA$46:$AA$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6047383616090158E-4</c:v>
+                  <c:v>3.9068531065444834E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4725691639655425E-3</c:v>
+                  <c:v>2.2080403737839704E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.0526798065406711E-3</c:v>
+                  <c:v>6.0728564632405169E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.3015983231291557E-3</c:v>
+                  <c:v>1.2426517915056889E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4457301707143433E-2</c:v>
+                  <c:v>2.1607382578832435E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.2710152073991408E-2</c:v>
+                  <c:v>3.387108312819298E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.3208768036646408E-2</c:v>
+                  <c:v>4.9397275753695125E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.1341346331093671E-2</c:v>
+                  <c:v>9.0586216013680221E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.9265545622292617E-2</c:v>
+                  <c:v>0.14513967165580799</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.12186000758037818</c:v>
+                  <c:v>0.17710270545299744</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.2118808427624056</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.24916612484925771</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.28859828229016504</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.32977374367537338</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.37225597414923339</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.41558682244261425</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.45929848629782655</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.14677954980803987</c:v>
+                  <c:v>0.502925659907554</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.17390643552859331</c:v>
+                  <c:v>0.54601740578214697</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.20308878331688196</c:v>
+                  <c:v>0.58814829868006924</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.23414310797727356</c:v>
+                  <c:v>0.62892842066016752</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.26685750664344243</c:v>
+                  <c:v>0.66801184199679575</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.30099545432818064</c:v>
+                  <c:v>0.70510329902060831</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.33630014372623185</c:v>
+                  <c:v>0.73996287183624077</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.77240856616549414</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.37249927814702655</c:v>
+                  <c:v>0.8023168075083541</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.40931020460858203</c:v>
+                  <c:v>0.82962095557805693</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.44644525704044258</c:v>
+                  <c:v>0.85430803621032092</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.48361716786090825</c:v>
+                  <c:v>0.87641396131764537</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.89601756099471075</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.52054440040464034</c:v>
+                  <c:v>0.91323378327537441</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.5569562550548135</c:v>
+                  <c:v>0.92820642575582757</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.5925976084864446</c:v>
+                  <c:v>0.94110075050063302</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.62723315787080081</c:v>
+                  <c:v>0.95209630200705619</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.66065105964988946</c:v>
+                  <c:v>0.96138020135541458</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.69266587471956798</c:v>
+                  <c:v>0.9691411326117827</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.97556417497427961</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.72312075748541671</c:v>
+                  <c:v>0.98082657083717228</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.75188885403185535</c:v>
+                  <c:v>0.98509446015102475</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.77887390322665384</c:v>
+                  <c:v>0.98852055864309485</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.99124271410354214</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.80401006260267238</c:v>
+                  <c:v>0.99338324245368448</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.82726100700728289</c:v>
+                  <c:v>0.99504892408153423</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.84861837111219418</c:v>
+                  <c:v>0.99730874997545671</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.86809962595736223</c:v>
+                  <c:v>0.99859473730011838</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.88574549403919223</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.90161701660824767</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.91579239067798501</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.92836369192022972</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.93943359356008671</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.94911218123412744</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.9575139503645862</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.96475505686229612</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.97095087488040932</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.98065200211710901</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.98745400781789527</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.99</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3790,10 +3648,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$Y$46:$Y$104</c:f>
+              <c:f>'Forestry input data'!$Y$46:$Y$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3827,112 +3685,112 @@
                 <c:pt idx="10">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="11">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="12">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="13">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="14">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="15">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="16">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="17">
                   <c:v>19</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="18">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="19">
                   <c:v>21</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="20">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="21">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="22">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="23">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="24">
                   <c:v>26</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="25">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="26">
                   <c:v>28</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="27">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="28">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="29">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="30">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="31">
                   <c:v>33</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="32">
                   <c:v>34</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="33">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="34">
                   <c:v>36</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="35">
                   <c:v>37</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="36">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="37">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="38">
                   <c:v>40</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="39">
                   <c:v>41</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="40">
                   <c:v>42</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="41">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="42">
                   <c:v>44</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="43">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="44">
                   <c:v>47</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="45">
                   <c:v>49</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="46">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -3940,150 +3798,150 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Forestry input data'!$AB$46:$AB$104</c:f>
+              <c:f>'Forestry input data'!$AB$46:$AB$92</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="47"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4736544540205898E-8</c:v>
+                  <c:v>2.2104816643775393E-8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7156931581859851E-7</c:v>
+                  <c:v>7.0735389035014862E-7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.58097392494372E-6</c:v>
+                  <c:v>5.3714560785955712E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.509010780864628E-5</c:v>
+                  <c:v>2.2635076320942638E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.6050641496542255E-5</c:v>
+                  <c:v>6.9075166990617554E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1458480543158345E-4</c:v>
+                  <c:v>1.7187228442427926E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.4764643556884902E-4</c:v>
+                  <c:v>3.7144665412003341E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.6979972652490023E-4</c:v>
+                  <c:v>1.3044158418094032E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3705211102403867E-3</c:v>
+                  <c:v>3.5536735681920284E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.6602089096390289E-3</c:v>
+                  <c:v>5.485286372002629E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.1737753221678977E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1818112028105343E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6645748005519212E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.2912020646323361E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.0898261197787602E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.0908267788234309E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.326278369249926E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.4566340453821027E-3</c:v>
+                  <c:v>6.8291623542396596E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.8943420713655232E-3</c:v>
+                  <c:v>8.6323130752672173E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1128182106990514E-2</c:v>
+                  <c:v>0.10767074244579511</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.5333611429249272E-2</c:v>
+                  <c:v>0.13261659831478967</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.0706402391637901E-2</c:v>
+                  <c:v>0.16139236976216209</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.7461585110137077E-2</c:v>
+                  <c:v>0.19415781223851813</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.5831438505938618E-2</c:v>
+                  <c:v>0.23097795355929318</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.27180030482823692</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.6062327716698603E-2</c:v>
+                  <c:v>0.31643397787364336</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.841018191920011E-2</c:v>
+                  <c:v>0.36453304803355158</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.3134418582571969E-2</c:v>
+                  <c:v>0.41558682244261402</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9.0490154268416667E-2</c:v>
+                  <c:v>0.46891975076157477</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.52370343131221975</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.11071860493424346</c:v>
+                  <c:v>0.57898242330021343</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.13403567663993465</c:v>
+                  <c:v>0.63371432892399926</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.16061888561034909</c:v>
+                  <c:v>0.68682289874110625</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.19059292691141783</c:v>
+                  <c:v>0.73726089850189358</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.22401443093002515</c:v>
+                  <c:v>0.78407744388738621</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.26085669689149504</c:v>
+                  <c:v>0.82648285744174654</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.86390327028919134</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.30099545432818042</c:v>
+                  <c:v>0.89601756099471053</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.34419694780889165</c:v>
+                  <c:v>0.92277098951020631</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.39010982776012937</c:v>
+                  <c:v>0.94436293999111653</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.96121007434763417</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.43826241244646302</c:v>
+                  <c:v>0.9738901576488701</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.48806681063370827</c:v>
+                  <c:v>0.98307494845487398</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.5388311126886246</c:v>
+                  <c:v>0.99371525106854153</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.58978033691130305</c:v>
+                  <c:v>0.99805805194152097</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6400860539065194</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.68890364347565436</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.7354150565882891</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.77887390322665351</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.81864885013023359</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.854260889277211</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.88541019911038366</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.91198915992692475</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.93407957479769954</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.96594413189444128</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.98443466735417506</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.99</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5818,15 +5676,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
+      <xdr:colOff>1057274</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5842,9 +5700,9 @@
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="9344025" y="7258050"/>
-          <a:ext cx="1428750" cy="342900"/>
+        <a:xfrm flipH="1">
+          <a:off x="9782174" y="9344025"/>
+          <a:ext cx="1562101" cy="66674"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5912,15 +5770,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>216086</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>161178</xdr:rowOff>
+      <xdr:colOff>209736</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>40527</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>63686</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>235325</xdr:rowOff>
+      <xdr:colOff>57336</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5937,8 +5795,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11309910" y="6089090"/>
-          <a:ext cx="4419600" cy="331882"/>
+          <a:off x="11325411" y="4964952"/>
+          <a:ext cx="4419600" cy="483347"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6017,13 +5875,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>1390649</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>224116</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>67235</xdr:rowOff>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6040,210 +5898,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="10086414" y="5514041"/>
-          <a:ext cx="1231526" cy="738841"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>56029</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="103" name="Rectangle 137">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11290674" y="5322794"/>
-          <a:ext cx="4419600" cy="661147"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFCC"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Note: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="sng" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Soil sub-group</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Used</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> in determination of forestry characteristic.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Peaty gley = Peaty Soils (5-50cm) e.g. peaty gley, peaty podsol</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Deep peat = Deep Peat (&gt;50cm) e.g. basin and blanket bogs</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1695450</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3501517" name="Line 112">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000CD6D3500}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="9982200" y="5686425"/>
-          <a:ext cx="790575" cy="219075"/>
+          <a:off x="10115549" y="5029200"/>
+          <a:ext cx="1209676" cy="161925"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6416,15 +6072,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>38099</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6441,8 +6097,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="10544174" y="6400800"/>
-          <a:ext cx="4200525" cy="476250"/>
+          <a:off x="11344274" y="8340725"/>
+          <a:ext cx="4410075" cy="476250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6504,15 +6160,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1152525</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>1155699</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6529,8 +6185,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm flipH="1">
-          <a:off x="9439275" y="7010400"/>
-          <a:ext cx="1333500" cy="95250"/>
+          <a:off x="9880599" y="8601075"/>
+          <a:ext cx="1482726" cy="654050"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6551,15 +6207,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>268941</xdr:rowOff>
+      <xdr:colOff>73025</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>183216</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6576,8 +6232,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11290674" y="9907493"/>
-          <a:ext cx="4419600" cy="1040654"/>
+          <a:off x="11341100" y="8896349"/>
+          <a:ext cx="4419600" cy="945217"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6667,296 +6323,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="Rectangle 137">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000021000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11325225" y="6362699"/>
-          <a:ext cx="4419600" cy="771525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFCC"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Note: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="sng" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Power curve</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr rtl="0"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" baseline="0">
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Based on Vestas 2.0MW Optispeed  turbine with roughness class C2, modelled over wind speed of 5-10 m s</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" baseline="30000">
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>. To define  a the power curve for a different turbine type, plot annual power output</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> , </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>P</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> (</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>MWh) against annual windspeed,</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> W (m</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> s</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="30000">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>) and  fit a linear regression  to obtain slope, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>a</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>, and intercept, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>b</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>P</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> = </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>aW</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> + </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="1" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>b</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Arial" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
@@ -8710,7 +8076,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>66</xdr:row>
-          <xdr:rowOff>82550</xdr:rowOff>
+          <xdr:rowOff>88900</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8768,7 +8134,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>66</xdr:row>
-          <xdr:rowOff>82550</xdr:rowOff>
+          <xdr:rowOff>88900</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8826,7 +8192,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8884,7 +8250,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8942,7 +8308,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9000,7 +8366,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9058,7 +8424,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9116,7 +8482,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9174,7 +8540,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9232,7 +8598,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9754,7 +9120,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>67</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9812,7 +9178,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>67</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10102,7 +9468,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>103</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10160,7 +9526,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>103</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10334,7 +9700,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>138</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10392,7 +9758,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>138</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10788,15 +10154,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>202184</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>25587</xdr:rowOff>
+      <xdr:colOff>208534</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>266886</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>164914</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>171264</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10813,8 +10179,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11270234" y="13541562"/>
-          <a:ext cx="4534730" cy="793563"/>
+          <a:off x="11324209" y="9925236"/>
+          <a:ext cx="4534730" cy="780863"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10907,15 +10273,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1117412</xdr:colOff>
+      <xdr:colOff>1114236</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>209549</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>64061</xdr:rowOff>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10931,9 +10297,9 @@
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="1">
-          <a:off x="9794687" y="13954125"/>
-          <a:ext cx="1482912" cy="254561"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9839136" y="10192310"/>
+          <a:ext cx="1495613" cy="113739"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -11174,7 +10540,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11232,7 +10598,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11290,7 +10656,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12380,7 +11746,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12438,7 +11804,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12494,7 +11860,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>1092200</xdr:colOff>
+          <xdr:colOff>1098550</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -12554,7 +11920,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12612,7 +11978,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12728,7 +12094,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12786,7 +12152,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12902,7 +12268,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12960,7 +12326,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13076,7 +12442,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13134,7 +12500,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13192,7 +12558,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>86</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13250,7 +12616,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>87</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13308,7 +12674,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>87</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14062,7 +13428,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>121</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14236,7 +13602,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14294,7 +13660,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14352,7 +13718,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14410,7 +13776,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>124</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14584,7 +13950,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14642,7 +14008,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14700,7 +14066,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14758,7 +14124,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14816,7 +14182,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14874,7 +14240,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14990,7 +14356,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>157</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15048,7 +14414,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>157</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15338,7 +14704,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15396,7 +14762,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15454,7 +14820,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15512,7 +14878,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15570,7 +14936,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15628,7 +14994,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15686,7 +15052,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15744,7 +15110,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15802,7 +15168,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15860,7 +15226,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15918,7 +15284,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15976,7 +15342,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16034,7 +15400,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16092,7 +15458,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16150,7 +15516,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16208,7 +15574,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16266,7 +15632,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16324,7 +15690,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16382,7 +15748,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16440,7 +15806,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16498,7 +15864,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16556,7 +15922,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16614,7 +15980,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16833,7 +16199,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16891,7 +16257,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16947,7 +16313,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>1092200</xdr:colOff>
+          <xdr:colOff>1098550</xdr:colOff>
           <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -17007,7 +16373,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17065,7 +16431,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17471,7 +16837,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17529,7 +16895,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17587,7 +16953,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17645,7 +17011,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17703,7 +17069,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17761,7 +17127,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17819,7 +17185,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>124</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18225,7 +17591,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>159</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18283,7 +17649,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>159</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18341,7 +17707,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18399,7 +17765,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18457,7 +17823,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18515,7 +17881,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18573,7 +17939,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18621,15 +17987,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>165660</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>126440</xdr:rowOff>
+      <xdr:colOff>225985</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>50240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>13260</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:colOff>73585</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -18646,8 +18012,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11240060" y="10775390"/>
-          <a:ext cx="4438650" cy="476810"/>
+          <a:off x="11341660" y="7803590"/>
+          <a:ext cx="4419600" cy="470460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18728,15 +18094,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1241425</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>26708</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>165660</xdr:colOff>
+      <xdr:colOff>225985</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>117195</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -18752,9 +18118,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="9921875" y="10991850"/>
-          <a:ext cx="1318185" cy="21945"/>
+        <a:xfrm flipH="1">
+          <a:off x="9915525" y="8037233"/>
+          <a:ext cx="1426135" cy="354292"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -18786,15 +18152,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>159580</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:colOff>200855</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -18811,8 +18177,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11268075" y="14725650"/>
-          <a:ext cx="4531555" cy="292100"/>
+          <a:off x="11350625" y="11087100"/>
+          <a:ext cx="4537905" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18925,15 +18291,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1162049</xdr:colOff>
+      <xdr:colOff>1162048</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>82549</xdr:rowOff>
+      <xdr:rowOff>85723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>209549</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -18950,8 +18316,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="9839324" y="14712949"/>
-          <a:ext cx="1438275" cy="136525"/>
+          <a:off x="9886948" y="10525123"/>
+          <a:ext cx="1476376" cy="685801"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -18972,15 +18338,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>159580</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>53975</xdr:rowOff>
+      <xdr:colOff>191330</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -18997,8 +18363,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11268075" y="14389100"/>
-          <a:ext cx="4531555" cy="295275"/>
+          <a:off x="11341100" y="10772775"/>
+          <a:ext cx="4537905" cy="215900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -19101,15 +18467,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1171574</xdr:colOff>
+      <xdr:colOff>1174748</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>222248</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -19125,9 +18491,9 @@
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="1">
-          <a:off x="9848849" y="14531975"/>
-          <a:ext cx="1441449" cy="3175"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="9899648" y="10344149"/>
+          <a:ext cx="1444626" cy="504825"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -19412,15 +18778,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -19437,8 +18803,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11312525" y="5226050"/>
-          <a:ext cx="4413250" cy="428625"/>
+          <a:off x="11325225" y="2619375"/>
+          <a:ext cx="4410075" cy="428625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20207,9 +19573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet1">
-    <tabColor rgb="FFFF99CC"/>
-  </sheetPr>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AB267"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20229,27 +19593,27 @@
     <col min="22" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="245"/>
-      <c r="C2" s="247" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="249" t="s">
+    <row r="1" spans="1:23" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="266"/>
+      <c r="C2" s="268" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="270" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="250"/>
-      <c r="F2" s="251" t="s">
+      <c r="E2" s="271"/>
+      <c r="F2" s="272" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="252"/>
-      <c r="H2" s="252"/>
-      <c r="I2" s="252"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="273"/>
+      <c r="I2" s="273"/>
       <c r="J2" s="42"/>
     </row>
-    <row r="3" spans="1:21" ht="38" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="246"/>
-      <c r="C3" s="248"/>
+    <row r="3" spans="1:23" ht="38" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="267"/>
+      <c r="C3" s="269"/>
       <c r="D3" s="32" t="s">
         <v>6</v>
       </c>
@@ -20271,10 +19635,10 @@
       <c r="J3" s="44"/>
       <c r="L3" s="38"/>
     </row>
-    <row r="4" spans="1:21" ht="13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="13" x14ac:dyDescent="0.2">
       <c r="B4" s="35"/>
       <c r="C4" s="51" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="166"/>
@@ -20285,10 +19649,10 @@
       <c r="J4" s="53"/>
       <c r="L4" s="41"/>
     </row>
-    <row r="5" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B5" s="49"/>
-      <c r="C5" s="217" t="s">
-        <v>47</v>
+      <c r="C5" s="215" t="s">
+        <v>43</v>
       </c>
       <c r="D5" s="154">
         <v>0.22500000000000001</v>
@@ -20297,7 +19661,7 @@
       <c r="F5" s="156">
         <v>0.22500000000000001</v>
       </c>
-      <c r="G5" s="216"/>
+      <c r="G5" s="214"/>
       <c r="H5" s="154">
         <v>0.22500000000000001</v>
       </c>
@@ -20305,10 +19669,10 @@
       <c r="J5" s="50"/>
       <c r="L5" s="41"/>
     </row>
-    <row r="6" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B6" s="49"/>
       <c r="C6" s="102" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D6" s="7">
         <v>3.32</v>
@@ -20325,10 +19689,10 @@
       <c r="J6" s="50"/>
       <c r="L6" s="41"/>
     </row>
-    <row r="7" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="30"/>
       <c r="C7" s="200" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D7" s="7">
         <v>39.33</v>
@@ -20345,10 +19709,10 @@
       <c r="J7" s="50"/>
       <c r="L7" s="41"/>
     </row>
-    <row r="8" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B8" s="30"/>
       <c r="C8" s="102" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8" s="198">
         <v>302.8</v>
@@ -20365,10 +19729,10 @@
       <c r="J8" s="50"/>
       <c r="L8" s="41"/>
     </row>
-    <row r="9" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B9" s="30"/>
       <c r="C9" s="102" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D9" s="7">
         <v>0.91</v>
@@ -20385,10 +19749,10 @@
       <c r="J9" s="50"/>
       <c r="L9" s="41"/>
     </row>
-    <row r="10" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B10" s="30"/>
       <c r="C10" s="102" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D10" s="7">
         <v>25.5</v>
@@ -20405,10 +19769,10 @@
       <c r="J10" s="50"/>
       <c r="L10" s="41"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B11" s="30"/>
       <c r="C11" s="102" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D11" s="7">
         <v>385.25</v>
@@ -20425,10 +19789,10 @@
       <c r="J11" s="50"/>
       <c r="L11" s="41"/>
     </row>
-    <row r="12" spans="1:21" ht="15.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B12" s="30"/>
       <c r="C12" s="102" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D12" s="7">
         <v>1516.42</v>
@@ -20445,10 +19809,10 @@
       <c r="J12" s="50"/>
       <c r="L12" s="41"/>
     </row>
-    <row r="13" spans="1:21" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A13" s="132"/>
       <c r="C13" s="102" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D13" s="7">
         <v>417.46</v>
@@ -20463,11 +19827,15 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="T13" s="221"/>
+      <c r="U13" s="221"/>
+      <c r="V13" s="221"/>
+      <c r="W13" s="221"/>
+    </row>
+    <row r="14" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B14" s="30"/>
       <c r="C14" s="102" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D14" s="7">
         <v>1983.37</v>
@@ -20483,14 +19851,15 @@
       <c r="I14" s="9"/>
       <c r="J14" s="50"/>
       <c r="L14" s="41"/>
-      <c r="U14" s="211" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T14" s="221"/>
+      <c r="U14" s="264"/>
+      <c r="V14" s="221"/>
+      <c r="W14" s="221"/>
+    </row>
+    <row r="15" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="45"/>
       <c r="C15" s="46" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D15" s="34"/>
       <c r="E15" s="166"/>
@@ -20502,16 +19871,17 @@
       <c r="L15" s="54"/>
       <c r="M15" s="4"/>
       <c r="O15" s="40"/>
-      <c r="U15" s="212" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T15" s="221"/>
+      <c r="U15" s="265"/>
+      <c r="V15" s="221"/>
+      <c r="W15" s="221"/>
+    </row>
+    <row r="16" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="30"/>
       <c r="C16" s="102" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="213">
+        <v>92</v>
+      </c>
+      <c r="D16" s="211">
         <v>0.34</v>
       </c>
       <c r="E16" s="207"/>
@@ -20523,18 +19893,21 @@
         <v>0.5</v>
       </c>
       <c r="I16" s="210"/>
-      <c r="J16" s="220"/>
+      <c r="J16" s="218"/>
       <c r="L16" s="54"/>
       <c r="M16" s="4"/>
       <c r="O16" s="40"/>
-      <c r="U16" s="212"/>
-    </row>
-    <row r="17" spans="2:21" ht="15.5" x14ac:dyDescent="0.2">
+      <c r="T16" s="221"/>
+      <c r="U16" s="265"/>
+      <c r="V16" s="221"/>
+      <c r="W16" s="221"/>
+    </row>
+    <row r="17" spans="2:23" ht="15.5" x14ac:dyDescent="0.2">
       <c r="B17" s="30"/>
       <c r="C17" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" s="213">
+        <v>91</v>
+      </c>
+      <c r="D17" s="211">
         <v>0.33800000000000002</v>
       </c>
       <c r="E17" s="207"/>
@@ -20550,14 +19923,15 @@
       <c r="L17" s="54"/>
       <c r="M17" s="4"/>
       <c r="O17" s="40"/>
-      <c r="U17" s="212" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="T17" s="221"/>
+      <c r="U17" s="265"/>
+      <c r="V17" s="221"/>
+      <c r="W17" s="221"/>
+    </row>
+    <row r="18" spans="2:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="203"/>
-      <c r="C18" s="218" t="s">
-        <v>104</v>
+      <c r="C18" s="216" t="s">
+        <v>94</v>
       </c>
       <c r="D18" s="208">
         <v>0.6</v>
@@ -20575,14 +19949,17 @@
       <c r="L18" s="54"/>
       <c r="M18" s="4"/>
       <c r="O18" s="40"/>
-      <c r="U18" s="212"/>
-    </row>
-    <row r="19" spans="2:21" ht="13" x14ac:dyDescent="0.2">
+      <c r="T18" s="221"/>
+      <c r="U18" s="265"/>
+      <c r="V18" s="221"/>
+      <c r="W18" s="221"/>
+    </row>
+    <row r="19" spans="2:23" ht="13" x14ac:dyDescent="0.2">
       <c r="B19" s="201"/>
       <c r="C19" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="219"/>
+        <v>95</v>
+      </c>
+      <c r="D19" s="217"/>
       <c r="E19" s="166"/>
       <c r="F19" s="204"/>
       <c r="G19" s="186"/>
@@ -20592,12 +19969,15 @@
       <c r="L19" s="54"/>
       <c r="M19" s="4"/>
       <c r="O19" s="40"/>
-      <c r="U19" s="212"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T19" s="221"/>
+      <c r="U19" s="265"/>
+      <c r="V19" s="221"/>
+      <c r="W19" s="221"/>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" s="30"/>
       <c r="C20" s="102" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D20" s="208">
         <v>0.61799999999999999</v>
@@ -20615,12 +19995,15 @@
       <c r="L20" s="54"/>
       <c r="M20" s="4"/>
       <c r="O20" s="40"/>
-      <c r="U20" s="212"/>
-    </row>
-    <row r="21" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="T20" s="221"/>
+      <c r="U20" s="265"/>
+      <c r="V20" s="221"/>
+      <c r="W20" s="221"/>
+    </row>
+    <row r="21" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="203"/>
       <c r="C21" s="102" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D21" s="208">
         <v>0.06</v>
@@ -20638,14 +20021,17 @@
       <c r="L21" s="54"/>
       <c r="M21" s="4"/>
       <c r="O21" s="40"/>
-      <c r="U21" s="212"/>
-    </row>
-    <row r="22" spans="2:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T21" s="221"/>
+      <c r="U21" s="265"/>
+      <c r="V21" s="221"/>
+      <c r="W21" s="221"/>
+    </row>
+    <row r="22" spans="2:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="201"/>
       <c r="C22" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="219"/>
+      <c r="D22" s="217"/>
       <c r="E22" s="166"/>
       <c r="F22" s="204"/>
       <c r="G22" s="186"/>
@@ -20655,14 +20041,15 @@
       <c r="L22" s="54"/>
       <c r="M22" s="4"/>
       <c r="O22" s="40"/>
-      <c r="U22" s="212" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" ht="13" x14ac:dyDescent="0.25">
+      <c r="T22" s="221"/>
+      <c r="U22" s="265"/>
+      <c r="V22" s="221"/>
+      <c r="W22" s="221"/>
+    </row>
+    <row r="23" spans="2:23" ht="13" x14ac:dyDescent="0.25">
       <c r="B23" s="55"/>
       <c r="C23" s="56" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D23" s="57"/>
       <c r="E23" s="167"/>
@@ -20671,11 +20058,12 @@
       <c r="H23" s="164"/>
       <c r="I23" s="58"/>
       <c r="J23" s="59"/>
-      <c r="U23" s="212" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T23" s="221"/>
+      <c r="U23" s="265"/>
+      <c r="V23" s="221"/>
+      <c r="W23" s="221"/>
+    </row>
+    <row r="24" spans="2:23" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="60"/>
       <c r="C24" s="61" t="s">
         <v>31</v>
@@ -20690,24 +20078,25 @@
       <c r="L24" s="54"/>
       <c r="M24" s="4"/>
       <c r="O24" s="40"/>
-      <c r="U24" s="212" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T24" s="221"/>
+      <c r="U24" s="265"/>
+      <c r="V24" s="221"/>
+      <c r="W24" s="221"/>
+    </row>
+    <row r="25" spans="2:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="67"/>
-      <c r="C25" s="267" t="s">
-        <v>86</v>
+      <c r="C25" s="237" t="s">
+        <v>82</v>
       </c>
       <c r="D25" s="156">
         <v>2</v>
       </c>
       <c r="E25" s="165"/>
-      <c r="F25" s="268">
+      <c r="F25" s="238">
         <v>2</v>
       </c>
       <c r="G25" s="171"/>
-      <c r="H25" s="269">
+      <c r="H25" s="239">
         <v>2</v>
       </c>
       <c r="I25" s="8"/>
@@ -20716,7 +20105,7 @@
       <c r="M25" s="4"/>
       <c r="O25" s="40"/>
     </row>
-    <row r="26" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="69"/>
       <c r="C26" s="48" t="s">
         <v>9</v>
@@ -20731,19 +20120,19 @@
       <c r="I26" s="9"/>
       <c r="J26" s="66"/>
       <c r="L26" s="153" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M26" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="69"/>
       <c r="C27" s="102" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D27" s="118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E27" s="165"/>
       <c r="F27" s="118"/>
@@ -20752,34 +20141,34 @@
       <c r="I27" s="9"/>
       <c r="J27" s="66"/>
       <c r="L27" s="153" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M27" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="69"/>
       <c r="C28" s="48" t="str">
         <f>IF(D27="Average height and age","Average tree height (m)","Yield class")</f>
         <v>Yield class</v>
       </c>
       <c r="D28" s="125">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" s="165"/>
       <c r="F28" s="118">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="171"/>
       <c r="H28" s="118">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="66"/>
       <c r="M28" s="4"/>
     </row>
-    <row r="29" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="69"/>
       <c r="C29" s="48" t="str">
         <f>IF(D27="Average height and age","Stand age (yr)","")</f>
@@ -20794,10 +20183,10 @@
       <c r="J29" s="66"/>
       <c r="M29" s="4"/>
     </row>
-    <row r="30" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="69"/>
       <c r="C30" s="48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D30" s="198">
         <v>0.4</v>
@@ -20814,10 +20203,10 @@
       <c r="J30" s="66"/>
       <c r="M30" s="4"/>
     </row>
-    <row r="31" spans="2:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="69"/>
       <c r="C31" s="102" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D31" s="156">
         <v>2</v>
@@ -20830,7 +20219,7 @@
       <c r="J31" s="66"/>
       <c r="M31" s="4"/>
     </row>
-    <row r="32" spans="2:21" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="69"/>
       <c r="C32" s="48" t="str">
         <f>IF(D31=1,"Length of rotation (yr) (50 yr default)","")</f>
@@ -20840,7 +20229,7 @@
       <c r="E32" s="169"/>
       <c r="F32" s="155"/>
       <c r="G32" s="188"/>
-      <c r="H32" s="270"/>
+      <c r="H32" s="10"/>
       <c r="I32" s="9"/>
       <c r="J32" s="66"/>
       <c r="M32" s="4"/>
@@ -20848,7 +20237,7 @@
     <row r="33" spans="2:28" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="69"/>
       <c r="C33" s="102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D33" s="11">
         <v>1</v>
@@ -20961,7 +20350,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="66"/>
       <c r="L38" s="70" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M38" s="4"/>
     </row>
@@ -20971,35 +20360,35 @@
         <f>IF($D$33=1, "Efficiency of the biomass power plant", "")</f>
         <v>Efficiency of the biomass power plant</v>
       </c>
-      <c r="D39" s="275">
+      <c r="D39" s="154">
         <v>0.35199999999999998</v>
       </c>
       <c r="E39" s="171"/>
-      <c r="F39" s="275">
+      <c r="F39" s="154">
         <v>0.35199999999999998</v>
       </c>
       <c r="G39" s="171"/>
-      <c r="H39" s="275">
+      <c r="H39" s="154">
         <v>0.35199999999999998</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="66"/>
       <c r="L39" s="70" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="150"/>
       <c r="C40" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="271"/>
-      <c r="E40" s="272"/>
-      <c r="F40" s="273"/>
+        <v>46</v>
+      </c>
+      <c r="D40" s="240"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="242"/>
       <c r="G40" s="185"/>
-      <c r="H40" s="273"/>
-      <c r="I40" s="274"/>
+      <c r="H40" s="242"/>
+      <c r="I40" s="243"/>
       <c r="J40" s="66"/>
       <c r="L40" s="70"/>
       <c r="M40" s="4"/>
@@ -21007,7 +20396,7 @@
     <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="71"/>
       <c r="C41" s="127" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D41" s="6">
         <v>50</v>
@@ -21028,7 +20417,7 @@
     <row r="42" spans="2:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="71"/>
       <c r="C42" s="127" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D42" s="6">
         <v>1</v>
@@ -21067,28 +20456,28 @@
     </row>
     <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B44" s="151"/>
-      <c r="C44" s="276" t="s">
+      <c r="C44" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="277">
+      <c r="D44" s="245">
         <v>0.5</v>
       </c>
       <c r="E44" s="165"/>
-      <c r="F44" s="278">
+      <c r="F44" s="246">
         <v>0.5</v>
       </c>
       <c r="G44" s="171"/>
-      <c r="H44" s="278">
+      <c r="H44" s="246">
         <v>0.5</v>
       </c>
-      <c r="I44" s="279"/>
+      <c r="I44" s="247"/>
       <c r="J44" s="152"/>
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="2:28" ht="13" x14ac:dyDescent="0.2">
       <c r="B45" s="73"/>
       <c r="C45" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="165"/>
@@ -21102,35 +20491,35 @@
         <v>13</v>
       </c>
       <c r="V45" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="X45" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="X45" s="113" t="s">
-        <v>64</v>
-      </c>
       <c r="Y45" s="113" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Z45" s="113" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AA45" s="113" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AB45" s="106" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="2:28" ht="25" x14ac:dyDescent="0.2">
       <c r="B46" s="73"/>
       <c r="C46" s="161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D46" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" s="116"/>
       <c r="F46" s="115">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G46" s="117"/>
       <c r="H46" s="115">
@@ -21140,7 +20529,7 @@
       <c r="J46" s="66"/>
       <c r="M46" s="4"/>
       <c r="U46" s="104" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="V46" s="5">
         <v>0</v>
@@ -21168,27 +20557,27 @@
     <row r="47" spans="2:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="73"/>
       <c r="C47" s="161" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D47" s="6">
         <v>50</v>
       </c>
       <c r="E47" s="103"/>
       <c r="F47" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="6">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="66"/>
       <c r="L47" s="70" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M47" s="4"/>
       <c r="U47" s="105" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V47" s="5">
         <v>1</v>
@@ -21202,41 +20591,41 @@
       </c>
       <c r="Z47" s="2">
         <f t="shared" si="1"/>
-        <v>8.7989160644090236E-2</v>
+        <v>0.1290364100439193</v>
       </c>
       <c r="AA47" s="2">
         <f t="shared" si="2"/>
-        <v>2.6047383616090158E-4</v>
+        <v>3.9068531065444834E-4</v>
       </c>
       <c r="AB47" s="3">
         <f t="shared" si="3"/>
-        <v>1.4736544540205898E-8</v>
+        <v>2.2104816643775393E-8</v>
       </c>
     </row>
     <row r="48" spans="2:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="73"/>
       <c r="C48" s="161" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D48" s="208">
-        <v>1.5</v>
-      </c>
-      <c r="E48" s="214"/>
+        <v>3</v>
+      </c>
+      <c r="E48" s="212"/>
       <c r="F48" s="208">
-        <v>1</v>
-      </c>
-      <c r="G48" s="215"/>
+        <v>3</v>
+      </c>
+      <c r="G48" s="213"/>
       <c r="H48" s="208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="66"/>
       <c r="L48" s="70" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M48" s="4"/>
       <c r="U48" s="105" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="V48" s="5">
         <v>1</v>
@@ -21250,42 +20639,42 @@
       </c>
       <c r="Z48" s="2">
         <f t="shared" si="1"/>
-        <v>0.16823622889732903</v>
+        <v>0.24142242497081623</v>
       </c>
       <c r="AA48" s="2">
         <f t="shared" si="2"/>
-        <v>1.4725691639655425E-3</v>
+        <v>2.2080403737839704E-3</v>
       </c>
       <c r="AB48" s="3">
         <f t="shared" si="3"/>
-        <v>4.7156931581859851E-7</v>
+        <v>7.0735389035014862E-7</v>
       </c>
     </row>
     <row r="49" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B49" s="73"/>
       <c r="C49" s="161" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D49" s="7">
         <v>0.5</v>
       </c>
       <c r="E49" s="158"/>
       <c r="F49" s="7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G49" s="159"/>
       <c r="H49" s="7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="66"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4"/>
       <c r="U49" s="105" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="V49" s="5">
-        <v>0.99</v>
+        <v>0.999</v>
       </c>
       <c r="X49" s="2">
         <v>3</v>
@@ -21296,21 +20685,21 @@
       </c>
       <c r="Z49" s="2">
         <f t="shared" si="1"/>
-        <v>0.24142242497081623</v>
+        <v>0.339306551992404</v>
       </c>
       <c r="AA49" s="2">
         <f t="shared" si="2"/>
-        <v>4.0526798065406711E-3</v>
+        <v>6.0728564632405169E-3</v>
       </c>
       <c r="AB49" s="3">
         <f t="shared" si="3"/>
-        <v>3.58097392494372E-6</v>
+        <v>5.3714560785955712E-6</v>
       </c>
     </row>
     <row r="50" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B50" s="73"/>
       <c r="C50" s="161" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D50" s="7">
         <v>0.05</v>
@@ -21328,7 +20717,7 @@
       <c r="L50" s="1"/>
       <c r="M50" s="4"/>
       <c r="U50" s="108" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="V50" s="109">
         <v>1</v>
@@ -21342,21 +20731,21 @@
       </c>
       <c r="Z50" s="2">
         <f t="shared" si="1"/>
-        <v>0.30816902908106347</v>
+        <v>0.42456006266284307</v>
       </c>
       <c r="AA50" s="2">
         <f t="shared" si="2"/>
-        <v>8.3015983231291557E-3</v>
+        <v>1.2426517915056889E-2</v>
       </c>
       <c r="AB50" s="3">
         <f t="shared" si="3"/>
-        <v>1.509010780864628E-5</v>
+        <v>2.2635076320942638E-5</v>
       </c>
     </row>
     <row r="51" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B51" s="73"/>
       <c r="C51" s="47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="158"/>
@@ -21368,7 +20757,7 @@
       <c r="L51" s="1"/>
       <c r="M51" s="4"/>
       <c r="U51" s="108" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="V51" s="109">
         <v>2.5</v>
@@ -21382,21 +20771,21 @@
       </c>
       <c r="Z51" s="2">
         <f t="shared" si="1"/>
-        <v>0.36904265551980675</v>
+        <v>0.49881276637272765</v>
       </c>
       <c r="AA51" s="2">
         <f t="shared" si="2"/>
-        <v>1.4457301707143433E-2</v>
+        <v>2.1607382578832435E-2</v>
       </c>
       <c r="AB51" s="3">
         <f t="shared" si="3"/>
-        <v>4.6050641496542255E-5</v>
+        <v>6.9075166990617554E-5</v>
       </c>
     </row>
     <row r="52" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B52" s="73"/>
       <c r="C52" s="161" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D52" s="11">
         <v>1</v>
@@ -21410,7 +20799,7 @@
       <c r="L52" s="1"/>
       <c r="M52" s="4"/>
       <c r="U52" s="110" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="V52" s="111">
         <v>5</v>
@@ -21424,21 +20813,21 @@
       </c>
       <c r="Z52" s="2">
         <f t="shared" si="1"/>
-        <v>0.42456006266284307</v>
+        <v>0.56348416775983401</v>
       </c>
       <c r="AA52" s="2">
         <f t="shared" si="2"/>
-        <v>2.2710152073991408E-2</v>
+        <v>3.387108312819298E-2</v>
       </c>
       <c r="AB52" s="3">
         <f t="shared" si="3"/>
-        <v>1.1458480543158345E-4</v>
+        <v>1.7187228442427926E-4</v>
       </c>
     </row>
     <row r="53" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B53" s="73"/>
       <c r="C53" s="161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D53" s="11">
         <v>1</v>
@@ -21460,21 +20849,21 @@
       </c>
       <c r="Z53" s="2">
         <f t="shared" si="1"/>
-        <v>0.47519253975022735</v>
+        <v>0.61981060367943874</v>
       </c>
       <c r="AA53" s="2">
         <f t="shared" si="2"/>
-        <v>3.3208768036646408E-2</v>
+        <v>4.9397275753695125E-2</v>
       </c>
       <c r="AB53" s="3">
         <f t="shared" si="3"/>
-        <v>2.4764643556884902E-4</v>
+        <v>3.7144665412003341E-4</v>
       </c>
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B54" s="73"/>
       <c r="C54" s="161" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D54" s="11">
         <v>1</v>
@@ -21496,21 +20885,21 @@
       </c>
       <c r="Z54" s="2">
         <f t="shared" si="1"/>
-        <v>0.56348416775983401</v>
+        <v>0.71159684968733927</v>
       </c>
       <c r="AA54" s="2">
         <f t="shared" si="2"/>
-        <v>6.1341346331093671E-2</v>
+        <v>9.0586216013680221E-2</v>
       </c>
       <c r="AB54" s="3">
         <f t="shared" si="3"/>
-        <v>8.6979972652490023E-4</v>
+        <v>1.3044158418094032E-3</v>
       </c>
     </row>
     <row r="55" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B55" s="73"/>
       <c r="C55" s="161" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D55" s="11">
         <v>2</v>
@@ -21532,21 +20921,21 @@
       </c>
       <c r="Z55" s="2">
         <f t="shared" si="1"/>
-        <v>0.63692194522989865</v>
+        <v>0.78122383760504466</v>
       </c>
       <c r="AA55" s="2">
         <f t="shared" si="2"/>
-        <v>9.9265545622292617E-2</v>
+        <v>0.14513967165580799</v>
       </c>
       <c r="AB55" s="3">
         <f t="shared" si="3"/>
-        <v>2.3705211102403867E-3</v>
+        <v>3.5536735681920284E-3</v>
       </c>
     </row>
     <row r="56" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B56" s="73"/>
       <c r="C56" s="161" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D56" s="11">
         <v>2</v>
@@ -21568,21 +20957,21 @@
       </c>
       <c r="Z56" s="2">
         <f t="shared" si="1"/>
-        <v>0.66886887851740884</v>
+        <v>0.80945392820367523</v>
       </c>
       <c r="AA56" s="2">
         <f t="shared" si="2"/>
-        <v>0.12186000758037818</v>
+        <v>0.17710270545299744</v>
       </c>
       <c r="AB56" s="3">
         <f t="shared" si="3"/>
-        <v>3.6602089096390289E-3</v>
+        <v>5.485286372002629E-3</v>
       </c>
     </row>
     <row r="57" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B57" s="73"/>
       <c r="C57" s="161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D57" s="11">
         <v>2</v>
@@ -21595,11 +20984,25 @@
       <c r="J57" s="66"/>
       <c r="L57" s="1"/>
       <c r="M57" s="4"/>
-      <c r="X57" s="2"/>
-      <c r="Y57" s="2"/>
-      <c r="Z57" s="2"/>
-      <c r="AA57" s="2"/>
-      <c r="AB57" s="3"/>
+      <c r="X57" s="2">
+        <v>13</v>
+      </c>
+      <c r="Y57" s="2">
+        <f t="shared" ref="Y57:Y63" si="4">IF(X57&lt;$D$47,X57,$D$47)</f>
+        <v>13</v>
+      </c>
+      <c r="Z57" s="2">
+        <f t="shared" ref="Z57:Z63" si="5">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y57,$V$50))</f>
+        <v>0.83404130925624387</v>
+      </c>
+      <c r="AA57" s="2">
+        <f t="shared" ref="AA57:AA63" si="6">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y57,$V$51))</f>
+        <v>0.2118808427624056</v>
+      </c>
+      <c r="AB57" s="3">
+        <f t="shared" ref="AB57:AB63" si="7">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y57,$V$52))</f>
+        <v>8.1737753221678977E-3</v>
+      </c>
     </row>
     <row r="58" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B58" s="74"/>
@@ -21613,11 +21016,25 @@
       <c r="J58" s="76"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="2"/>
-      <c r="AA58" s="2"/>
-      <c r="AB58" s="3"/>
+      <c r="X58" s="2">
+        <v>14</v>
+      </c>
+      <c r="Y58" s="2">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="Z58" s="2">
+        <f t="shared" si="5"/>
+        <v>0.85545602292540723</v>
+      </c>
+      <c r="AA58" s="2">
+        <f t="shared" si="6"/>
+        <v>0.24916612484925771</v>
+      </c>
+      <c r="AB58" s="3">
+        <f t="shared" si="7"/>
+        <v>1.1818112028105343E-2</v>
+      </c>
     </row>
     <row r="59" spans="2:28" ht="13" x14ac:dyDescent="0.2">
       <c r="B59" s="77"/>
@@ -21633,37 +21050,65 @@
       <c r="J59" s="79"/>
       <c r="L59" s="1"/>
       <c r="M59" s="4"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
-      <c r="AA59" s="2"/>
-      <c r="AB59" s="3"/>
+      <c r="X59" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y59" s="2">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="Z59" s="2">
+        <f t="shared" si="5"/>
+        <v>0.87410745882058327</v>
+      </c>
+      <c r="AA59" s="2">
+        <f t="shared" si="6"/>
+        <v>0.28859828229016504</v>
+      </c>
+      <c r="AB59" s="3">
+        <f t="shared" si="7"/>
+        <v>1.6645748005519212E-2</v>
+      </c>
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B60" s="81"/>
-      <c r="C60" s="267" t="s">
-        <v>86</v>
+      <c r="C60" s="237" t="s">
+        <v>82</v>
       </c>
       <c r="D60" s="156">
         <v>2</v>
       </c>
       <c r="E60" s="165"/>
-      <c r="F60" s="268">
+      <c r="F60" s="238">
         <v>2</v>
       </c>
       <c r="G60" s="171"/>
-      <c r="H60" s="269">
+      <c r="H60" s="239">
         <v>2</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="79"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4"/>
-      <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="2"/>
-      <c r="AA60" s="2"/>
-      <c r="AB60" s="3"/>
+      <c r="X60" s="2">
+        <v>16</v>
+      </c>
+      <c r="Y60" s="2">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="Z60" s="2">
+        <f t="shared" si="5"/>
+        <v>0.89035218038568142</v>
+      </c>
+      <c r="AA60" s="2">
+        <f t="shared" si="6"/>
+        <v>0.32977374367537338</v>
+      </c>
+      <c r="AB60" s="3">
+        <f t="shared" si="7"/>
+        <v>2.2912020646323361E-2</v>
+      </c>
     </row>
     <row r="61" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B61" s="82"/>
@@ -21681,19 +21126,33 @@
       <c r="J61" s="80"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4"/>
-      <c r="X61" s="2"/>
-      <c r="Y61" s="2"/>
-      <c r="Z61" s="2"/>
-      <c r="AA61" s="2"/>
-      <c r="AB61" s="3"/>
+      <c r="X61" s="2">
+        <v>17</v>
+      </c>
+      <c r="Y61" s="2">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="Z61" s="2">
+        <f t="shared" si="5"/>
+        <v>0.90450074139785641</v>
+      </c>
+      <c r="AA61" s="2">
+        <f t="shared" si="6"/>
+        <v>0.37225597414923339</v>
+      </c>
+      <c r="AB61" s="3">
+        <f t="shared" si="7"/>
+        <v>3.0898261197787602E-2</v>
+      </c>
     </row>
     <row r="62" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B62" s="124"/>
       <c r="C62" s="102" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D62" s="118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E62" s="165"/>
       <c r="F62" s="118"/>
@@ -21703,11 +21162,25 @@
       <c r="J62" s="123"/>
       <c r="L62" s="1"/>
       <c r="M62" s="4"/>
-      <c r="X62" s="2"/>
-      <c r="Y62" s="2"/>
-      <c r="Z62" s="2"/>
-      <c r="AA62" s="2"/>
-      <c r="AB62" s="3"/>
+      <c r="X62" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y62" s="2">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="Z62" s="2">
+        <f t="shared" si="5"/>
+        <v>0.91682362288973285</v>
+      </c>
+      <c r="AA62" s="2">
+        <f t="shared" si="6"/>
+        <v>0.41558682244261425</v>
+      </c>
+      <c r="AB62" s="3">
+        <f t="shared" si="7"/>
+        <v>4.0908267788234309E-2</v>
+      </c>
     </row>
     <row r="63" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B63" s="124"/>
@@ -21716,25 +21189,39 @@
         <v>Yield class</v>
       </c>
       <c r="D63" s="125">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E63" s="165"/>
       <c r="F63" s="118">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G63" s="171"/>
       <c r="H63" s="118">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="123"/>
       <c r="L63" s="1"/>
       <c r="M63" s="4"/>
-      <c r="X63" s="2"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="2"/>
-      <c r="AA63" s="2"/>
-      <c r="AB63" s="3"/>
+      <c r="X63" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y63" s="2">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="Z63" s="2">
+        <f t="shared" si="5"/>
+        <v>0.92755640399250094</v>
+      </c>
+      <c r="AA63" s="2">
+        <f t="shared" si="6"/>
+        <v>0.45929848629782655</v>
+      </c>
+      <c r="AB63" s="3">
+        <f t="shared" si="7"/>
+        <v>5.326278369249926E-2</v>
+      </c>
     </row>
     <row r="64" spans="2:28" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="124"/>
@@ -21751,29 +21238,29 @@
       <c r="J64" s="123"/>
       <c r="M64" s="4"/>
       <c r="X64" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y64" s="2">
-        <f t="shared" ref="Y64:Y70" si="4">IF(X64&lt;$D$47,X64,$D$47)</f>
-        <v>13</v>
+        <f>IF(X64&lt;$D$47,X64,$D$47)</f>
+        <v>20</v>
       </c>
       <c r="Z64" s="2">
-        <f t="shared" ref="Z64:Z70" si="5">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y64,$V$50))</f>
-        <v>0.69800482795979835</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y64,$V$50))</f>
+        <v>0.9369042655519807</v>
       </c>
       <c r="AA64" s="2">
-        <f t="shared" ref="AA64:AA70" si="6">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y64,$V$51))</f>
-        <v>0.14677954980803987</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y64,$V$51))</f>
+        <v>0.502925659907554</v>
       </c>
       <c r="AB64" s="3">
-        <f t="shared" ref="AB64:AB70" si="7">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y64,$V$52))</f>
-        <v>5.4566340453821027E-3</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y64,$V$52))</f>
+        <v>6.8291623542396596E-2</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="124"/>
       <c r="C65" s="48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D65" s="198">
         <v>0.4</v>
@@ -21792,29 +21279,29 @@
       <c r="M65" s="4"/>
       <c r="O65" s="40"/>
       <c r="X65" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y65" s="2">
-        <f t="shared" si="4"/>
-        <v>14</v>
+        <f>IF(X65&lt;$D$47,X65,$D$47)</f>
+        <v>21</v>
       </c>
       <c r="Z65" s="2">
-        <f t="shared" si="5"/>
-        <v>0.72457712966618337</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y65,$V$50))</f>
+        <v>0.94504591261423754</v>
       </c>
       <c r="AA65" s="2">
-        <f t="shared" si="6"/>
-        <v>0.17390643552859331</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y65,$V$51))</f>
+        <v>0.54601740578214697</v>
       </c>
       <c r="AB65" s="3">
-        <f t="shared" si="7"/>
-        <v>7.8943420713655232E-3</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y65,$V$52))</f>
+        <v>8.6323130752672173E-2</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B66" s="82"/>
       <c r="C66" s="48" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D66" s="11">
         <v>2</v>
@@ -21829,23 +21316,23 @@
       <c r="M66" s="4"/>
       <c r="O66" s="40"/>
       <c r="X66" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Y66" s="2">
-        <f t="shared" si="4"/>
-        <v>15</v>
+        <f>IF(X66&lt;$D$47,X66,$D$47)</f>
+        <v>22</v>
       </c>
       <c r="Z66" s="2">
-        <f t="shared" si="5"/>
-        <v>0.74881135684904199</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y66,$V$50))</f>
+        <v>0.95213699076773617</v>
       </c>
       <c r="AA66" s="2">
-        <f t="shared" si="6"/>
-        <v>0.20308878331688196</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y66,$V$51))</f>
+        <v>0.58814829868006924</v>
       </c>
       <c r="AB66" s="3">
-        <f t="shared" si="7"/>
-        <v>1.1128182106990514E-2</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y66,$V$52))</f>
+        <v>0.10767074244579511</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -21866,30 +21353,30 @@
       <c r="M67" s="4"/>
       <c r="O67" s="40"/>
       <c r="X67" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Y67" s="2">
-        <f t="shared" si="4"/>
-        <v>16</v>
+        <f>IF(X67&lt;$D$47,X67,$D$47)</f>
+        <v>23</v>
       </c>
       <c r="Z67" s="2">
-        <f t="shared" si="5"/>
-        <v>0.77091323472322271</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y67,$V$50))</f>
+        <v>0.95831306165296648</v>
       </c>
       <c r="AA67" s="2">
-        <f t="shared" si="6"/>
-        <v>0.23414310797727356</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y67,$V$51))</f>
+        <v>0.62892842066016752</v>
       </c>
       <c r="AB67" s="3">
-        <f t="shared" si="7"/>
-        <v>1.5333611429249272E-2</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y67,$V$52))</f>
+        <v>0.13261659831478967</v>
       </c>
     </row>
     <row r="68" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="132"/>
       <c r="B68" s="131"/>
       <c r="C68" s="102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D68" s="11">
         <v>2</v>
@@ -21904,23 +21391,23 @@
       <c r="M68" s="4"/>
       <c r="O68" s="40"/>
       <c r="X68" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y68" s="2">
-        <f t="shared" si="4"/>
-        <v>17</v>
+        <f t="shared" ref="Y68:Y73" si="8">IF(X68&lt;$D$47,X68,$D$47)</f>
+        <v>24</v>
       </c>
       <c r="Z68" s="2">
-        <f t="shared" si="5"/>
-        <v>0.79107038691459608</v>
+        <f t="shared" ref="Z68:Z73" si="9">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y68,$V$50))</f>
+        <v>0.96369219452298982</v>
       </c>
       <c r="AA68" s="2">
-        <f t="shared" si="6"/>
-        <v>0.26685750664344243</v>
+        <f t="shared" ref="AA68:AA73" si="10">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y68,$V$51))</f>
+        <v>0.66801184199679575</v>
       </c>
       <c r="AB68" s="3">
-        <f t="shared" si="7"/>
-        <v>2.0706402391637901E-2</v>
+        <f t="shared" ref="AB68:AB73" si="11">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y68,$V$52))</f>
+        <v>0.16139236976216209</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -21940,23 +21427,23 @@
       <c r="M69" s="4"/>
       <c r="O69" s="40"/>
       <c r="X69" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Y69" s="2">
-        <f t="shared" si="4"/>
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>25</v>
       </c>
       <c r="Z69" s="2">
-        <f t="shared" si="5"/>
-        <v>0.80945392820367523</v>
+        <f t="shared" si="9"/>
+        <v>0.96837722339831622</v>
       </c>
       <c r="AA69" s="2">
-        <f t="shared" si="6"/>
-        <v>0.30099545432818064</v>
+        <f t="shared" si="10"/>
+        <v>0.70510329902060831</v>
       </c>
       <c r="AB69" s="3">
-        <f t="shared" si="7"/>
-        <v>2.7461585110137077E-2</v>
+        <f t="shared" si="11"/>
+        <v>0.19415781223851813</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -21977,23 +21464,23 @@
       <c r="M70" s="4"/>
       <c r="O70" s="40"/>
       <c r="X70" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Y70" s="2">
-        <f t="shared" si="4"/>
-        <v>19</v>
+        <f t="shared" si="8"/>
+        <v>26</v>
       </c>
       <c r="Z70" s="2">
-        <f t="shared" si="5"/>
-        <v>0.82621991712506238</v>
+        <f t="shared" si="9"/>
+        <v>0.97245771296661832</v>
       </c>
       <c r="AA70" s="2">
-        <f t="shared" si="6"/>
-        <v>0.33630014372623185</v>
+        <f t="shared" si="10"/>
+        <v>0.73996287183624077</v>
       </c>
       <c r="AB70" s="3">
-        <f t="shared" si="7"/>
-        <v>3.5831438505938618E-2</v>
+        <f t="shared" si="11"/>
+        <v>0.23097795355929318</v>
       </c>
     </row>
     <row r="71" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -22013,11 +21500,25 @@
       <c r="L71" s="39"/>
       <c r="M71" s="4"/>
       <c r="O71" s="40"/>
-      <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-      <c r="Z71" s="2"/>
-      <c r="AA71" s="2"/>
-      <c r="AB71" s="3"/>
+      <c r="X71" s="2">
+        <v>27</v>
+      </c>
+      <c r="Y71" s="2">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="Z71" s="2">
+        <f t="shared" si="9"/>
+        <v>0.97601167080980511</v>
+      </c>
+      <c r="AA71" s="2">
+        <f t="shared" si="10"/>
+        <v>0.77240856616549414</v>
+      </c>
+      <c r="AB71" s="3">
+        <f t="shared" si="11"/>
+        <v>0.27180030482823692</v>
+      </c>
     </row>
     <row r="72" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="132"/>
@@ -22037,23 +21538,23 @@
       <c r="J72" s="80"/>
       <c r="M72" s="4"/>
       <c r="X72" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Y72" s="2">
-        <f>IF(X72&lt;$D$47,X72,$D$47)</f>
-        <v>20</v>
+        <f t="shared" si="8"/>
+        <v>28</v>
       </c>
       <c r="Z72" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y72,$V$50))</f>
-        <v>0.84151068075388857</v>
+        <f t="shared" si="9"/>
+        <v>0.97910703869145954</v>
       </c>
       <c r="AA72" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y72,$V$51))</f>
-        <v>0.37249927814702655</v>
+        <f t="shared" si="10"/>
+        <v>0.8023168075083541</v>
       </c>
       <c r="AB72" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y72,$V$52))</f>
-        <v>4.6062327716698603E-2</v>
+        <f t="shared" si="11"/>
+        <v>0.31643397787364336</v>
       </c>
     </row>
     <row r="73" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22071,23 +21572,23 @@
       <c r="J73" s="80"/>
       <c r="M73" s="4"/>
       <c r="X73" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Y73" s="2">
-        <f>IF(X73&lt;$D$47,X73,$D$47)</f>
-        <v>21</v>
+        <f t="shared" si="8"/>
+        <v>29</v>
       </c>
       <c r="Z73" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y73,$V$50))</f>
-        <v>0.85545602292540723</v>
+        <f t="shared" si="9"/>
+        <v>0.98180299141390015</v>
       </c>
       <c r="AA73" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y73,$V$51))</f>
-        <v>0.40931020460858203</v>
+        <f t="shared" si="10"/>
+        <v>0.82962095557805693</v>
       </c>
       <c r="AB73" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y73,$V$52))</f>
-        <v>5.841018191920011E-2</v>
+        <f t="shared" si="11"/>
+        <v>0.36453304803355158</v>
       </c>
     </row>
     <row r="74" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22096,71 +21597,71 @@
         <f>IF($D$68=1, "Efficiency of the biomass power plant", "")</f>
         <v/>
       </c>
-      <c r="D74" s="275"/>
+      <c r="D74" s="154"/>
       <c r="E74" s="171"/>
-      <c r="F74" s="275"/>
+      <c r="F74" s="154"/>
       <c r="G74" s="171"/>
-      <c r="H74" s="275"/>
+      <c r="H74" s="154"/>
       <c r="I74" s="9"/>
       <c r="J74" s="80"/>
       <c r="M74" s="4"/>
       <c r="X74" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y74" s="2">
         <f>IF(X74&lt;$D$47,X74,$D$47)</f>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Z74" s="2">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y74,$V$50))</f>
-        <v>0.8681743261443593</v>
+        <v>0.98415106807538888</v>
       </c>
       <c r="AA74" s="2">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y74,$V$51))</f>
-        <v>0.44644525704044258</v>
+        <v>0.85430803621032092</v>
       </c>
       <c r="AB74" s="3">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y74,$V$52))</f>
-        <v>7.3134418582571969E-2</v>
+        <v>0.41558682244261402</v>
       </c>
     </row>
     <row r="75" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="84"/>
       <c r="C75" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="271"/>
-      <c r="E75" s="272"/>
-      <c r="F75" s="273"/>
+        <v>46</v>
+      </c>
+      <c r="D75" s="240"/>
+      <c r="E75" s="241"/>
+      <c r="F75" s="242"/>
       <c r="G75" s="185"/>
-      <c r="H75" s="273"/>
-      <c r="I75" s="274"/>
+      <c r="H75" s="242"/>
+      <c r="I75" s="243"/>
       <c r="J75" s="80"/>
       <c r="M75" s="4"/>
       <c r="X75" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Y75" s="2">
         <f>IF(X75&lt;$D$47,X75,$D$47)</f>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Z75" s="2">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y75,$V$50))</f>
-        <v>0.87977355653825873</v>
+        <v>0.98619615735397115</v>
       </c>
       <c r="AA75" s="2">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y75,$V$51))</f>
-        <v>0.48361716786090825</v>
+        <v>0.87641396131764537</v>
       </c>
       <c r="AB75" s="3">
         <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y75,$V$52))</f>
-        <v>9.0490154268416667E-2</v>
+        <v>0.46891975076157477</v>
       </c>
     </row>
     <row r="76" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="85"/>
       <c r="C76" s="127" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D76" s="6">
         <v>50</v>
@@ -22176,16 +21677,30 @@
       <c r="I76" s="9"/>
       <c r="J76" s="80"/>
       <c r="M76" s="4"/>
-      <c r="X76" s="2"/>
-      <c r="Y76" s="2"/>
-      <c r="Z76" s="2"/>
-      <c r="AA76" s="2"/>
-      <c r="AB76" s="3"/>
+      <c r="X76" s="2">
+        <v>32</v>
+      </c>
+      <c r="Y76" s="2">
+        <f>IF(X76&lt;$D$47,X76,$D$47)</f>
+        <v>32</v>
+      </c>
+      <c r="Z76" s="2">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y76,$V$50))</f>
+        <v>0.98797735565382583</v>
+      </c>
+      <c r="AA76" s="2">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y76,$V$51))</f>
+        <v>0.89601756099471075</v>
+      </c>
+      <c r="AB76" s="3">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y76,$V$52))</f>
+        <v>0.52370343131221975</v>
+      </c>
     </row>
     <row r="77" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="85"/>
       <c r="C77" s="127" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D77" s="6">
         <v>1</v>
@@ -22203,23 +21718,23 @@
       <c r="L77" s="70"/>
       <c r="M77" s="4"/>
       <c r="X77" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Y77" s="2">
-        <f t="shared" ref="Y77:Y82" si="8">IF(X77&lt;$D$47,X77,$D$47)</f>
-        <v>24</v>
+        <f t="shared" ref="Y77:Y89" si="12">IF(X77&lt;$D$47,X77,$D$47)</f>
+        <v>33</v>
       </c>
       <c r="Z77" s="2">
-        <f t="shared" ref="Z77:Z82" si="9">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y77,$V$50))</f>
-        <v>0.89035218038568142</v>
+        <f t="shared" ref="Z77:Z89" si="13">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y77,$V$50))</f>
+        <v>0.98952871451949098</v>
       </c>
       <c r="AA77" s="2">
-        <f t="shared" ref="AA77:AA82" si="10">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y77,$V$51))</f>
-        <v>0.52054440040464034</v>
+        <f t="shared" ref="AA77:AA89" si="14">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y77,$V$51))</f>
+        <v>0.91323378327537441</v>
       </c>
       <c r="AB77" s="3">
-        <f t="shared" ref="AB77:AB82" si="11">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y77,$V$52))</f>
-        <v>0.11071860493424346</v>
+        <f t="shared" ref="AB77:AB89" si="15">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y77,$V$52))</f>
+        <v>0.57898242330021343</v>
       </c>
     </row>
     <row r="78" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -22244,29 +21759,29 @@
       <c r="L78" s="70"/>
       <c r="M78" s="4"/>
       <c r="X78" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Y78" s="2">
-        <f t="shared" si="8"/>
-        <v>25</v>
+        <f t="shared" si="12"/>
+        <v>34</v>
       </c>
       <c r="Z78" s="2">
-        <f t="shared" si="9"/>
-        <v>0.9</v>
+        <f t="shared" si="13"/>
+        <v>0.99087989160644085</v>
       </c>
       <c r="AA78" s="2">
-        <f t="shared" si="10"/>
-        <v>0.5569562550548135</v>
+        <f t="shared" si="14"/>
+        <v>0.92820642575582757</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="11"/>
-        <v>0.13403567663993465</v>
+        <f t="shared" si="15"/>
+        <v>0.63371432892399926</v>
       </c>
     </row>
     <row r="79" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="132"/>
       <c r="B79" s="84"/>
-      <c r="C79" s="276" t="s">
+      <c r="C79" s="244" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="12">
@@ -22280,34 +21795,34 @@
       <c r="H79" s="12">
         <v>0.5</v>
       </c>
-      <c r="I79" s="279"/>
+      <c r="I79" s="247"/>
       <c r="J79" s="80"/>
       <c r="L79" s="70"/>
       <c r="M79" s="4"/>
       <c r="X79" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Y79" s="2">
-        <f t="shared" si="8"/>
-        <v>26</v>
+        <f t="shared" si="12"/>
+        <v>35</v>
       </c>
       <c r="Z79" s="2">
-        <f t="shared" si="9"/>
-        <v>0.90879891606440899</v>
+        <f t="shared" si="13"/>
+        <v>0.99205671765275716</v>
       </c>
       <c r="AA79" s="2">
-        <f t="shared" si="10"/>
-        <v>0.5925976084864446</v>
+        <f t="shared" si="14"/>
+        <v>0.94110075050063302</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="11"/>
-        <v>0.16061888561034909</v>
+        <f t="shared" si="15"/>
+        <v>0.68682289874110625</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="160"/>
       <c r="C80" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D80" s="157"/>
       <c r="E80" s="165"/>
@@ -22319,37 +21834,37 @@
       <c r="L80" s="70"/>
       <c r="M80" s="4"/>
       <c r="X80" s="2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Y80" s="2">
-        <f t="shared" si="8"/>
-        <v>27</v>
+        <f t="shared" si="12"/>
+        <v>36</v>
       </c>
       <c r="Z80" s="2">
-        <f t="shared" si="9"/>
-        <v>0.91682362288973285</v>
+        <f t="shared" si="13"/>
+        <v>0.99308169029081061</v>
       </c>
       <c r="AA80" s="2">
-        <f t="shared" si="10"/>
-        <v>0.62723315787080081</v>
+        <f t="shared" si="14"/>
+        <v>0.95209630200705619</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="11"/>
-        <v>0.19059292691141783</v>
+        <f t="shared" si="15"/>
+        <v>0.73726089850189358</v>
       </c>
     </row>
     <row r="81" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="132"/>
       <c r="B81" s="160"/>
       <c r="C81" s="161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D81" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E81" s="116"/>
       <c r="F81" s="115">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G81" s="117"/>
       <c r="H81" s="115">
@@ -22360,74 +21875,74 @@
       <c r="L81" s="70"/>
       <c r="M81" s="4"/>
       <c r="X81" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Y81" s="2">
-        <f t="shared" si="8"/>
-        <v>28</v>
+        <f t="shared" si="12"/>
+        <v>37</v>
       </c>
       <c r="Z81" s="2">
-        <f t="shared" si="9"/>
-        <v>0.92414224249708166</v>
+        <f t="shared" si="13"/>
+        <v>0.99397440413925642</v>
       </c>
       <c r="AA81" s="2">
-        <f t="shared" si="10"/>
-        <v>0.66065105964988946</v>
+        <f t="shared" si="14"/>
+        <v>0.96138020135541458</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="11"/>
-        <v>0.22401443093002515</v>
+        <f t="shared" si="15"/>
+        <v>0.78407744388738621</v>
       </c>
     </row>
     <row r="82" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="132"/>
       <c r="B82" s="160"/>
       <c r="C82" s="161" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D82" s="6">
         <v>100</v>
       </c>
       <c r="E82" s="165"/>
       <c r="F82" s="10">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G82" s="171"/>
       <c r="H82" s="10">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="136"/>
       <c r="L82" s="70"/>
       <c r="M82" s="4"/>
       <c r="X82" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Y82" s="2">
-        <f t="shared" si="8"/>
-        <v>29</v>
+        <f t="shared" si="12"/>
+        <v>38</v>
       </c>
       <c r="Z82" s="2">
-        <f t="shared" si="9"/>
-        <v>0.93081690290810637</v>
+        <f t="shared" si="13"/>
+        <v>0.99475192539750223</v>
       </c>
       <c r="AA82" s="2">
-        <f t="shared" si="10"/>
-        <v>0.69266587471956798</v>
+        <f t="shared" si="14"/>
+        <v>0.9691411326117827</v>
       </c>
       <c r="AB82" s="3">
-        <f t="shared" si="11"/>
-        <v>0.26085669689149504</v>
+        <f t="shared" si="15"/>
+        <v>0.82648285744174654</v>
       </c>
     </row>
     <row r="83" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="132"/>
       <c r="B83" s="138"/>
       <c r="C83" s="161" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D83" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="103"/>
       <c r="F83" s="6">
@@ -22435,62 +21950,76 @@
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="136"/>
       <c r="L83" s="70"/>
       <c r="M83" s="4"/>
-      <c r="X83" s="2"/>
-      <c r="Y83" s="2"/>
-      <c r="Z83" s="2"/>
-      <c r="AA83" s="2"/>
-      <c r="AB83" s="3"/>
+      <c r="X83" s="2">
+        <v>39</v>
+      </c>
+      <c r="Y83" s="2">
+        <f t="shared" si="12"/>
+        <v>39</v>
+      </c>
+      <c r="Z83" s="2">
+        <f t="shared" si="13"/>
+        <v>0.99542911810385126</v>
+      </c>
+      <c r="AA83" s="2">
+        <f t="shared" si="14"/>
+        <v>0.97556417497427961</v>
+      </c>
+      <c r="AB83" s="3">
+        <f t="shared" si="15"/>
+        <v>0.86390327028919134</v>
+      </c>
     </row>
     <row r="84" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="160"/>
       <c r="C84" s="161" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D84" s="7">
         <v>0.5</v>
       </c>
       <c r="E84" s="158"/>
       <c r="F84" s="7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G84" s="159"/>
       <c r="H84" s="7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="136"/>
       <c r="M84" s="4"/>
       <c r="X84" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Y84" s="2">
-        <f>IF(X84&lt;$D$47,X84,$D$47)</f>
-        <v>30</v>
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="Z84" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y84,$V$50))</f>
-        <v>0.9369042655519807</v>
+        <f t="shared" si="13"/>
+        <v>0.99601892829446503</v>
       </c>
       <c r="AA84" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y84,$V$51))</f>
-        <v>0.72312075748541671</v>
+        <f t="shared" si="14"/>
+        <v>0.98082657083717228</v>
       </c>
       <c r="AB84" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y84,$V$52))</f>
-        <v>0.30099545432818042</v>
+        <f t="shared" si="15"/>
+        <v>0.89601756099471053</v>
       </c>
     </row>
     <row r="85" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="132"/>
       <c r="B85" s="138"/>
       <c r="C85" s="161" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D85" s="7">
         <v>0.05</v>
@@ -22507,29 +22036,29 @@
       <c r="J85" s="136"/>
       <c r="M85" s="4"/>
       <c r="X85" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Y85" s="2">
-        <f>IF(X85&lt;$D$47,X85,$D$47)</f>
-        <v>31</v>
+        <f t="shared" si="12"/>
+        <v>41</v>
       </c>
       <c r="Z85" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y85,$V$50))</f>
-        <v>0.94245600626628434</v>
+        <f t="shared" si="13"/>
+        <v>0.99653263149547466</v>
       </c>
       <c r="AA85" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y85,$V$51))</f>
-        <v>0.75188885403185535</v>
+        <f t="shared" si="14"/>
+        <v>0.98509446015102475</v>
       </c>
       <c r="AB85" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y85,$V$52))</f>
-        <v>0.34419694780889165</v>
+        <f t="shared" si="15"/>
+        <v>0.92277098951020631</v>
       </c>
     </row>
     <row r="86" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="160"/>
       <c r="C86" s="47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D86" s="7"/>
       <c r="E86" s="158"/>
@@ -22540,29 +22069,29 @@
       <c r="J86" s="136"/>
       <c r="M86" s="4"/>
       <c r="X86" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Y86" s="2">
-        <f>IF(X86&lt;$D$47,X86,$D$47)</f>
-        <v>32</v>
+        <f t="shared" si="12"/>
+        <v>42</v>
       </c>
       <c r="Z86" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y86,$V$50))</f>
-        <v>0.94751925397502268</v>
+        <f t="shared" si="13"/>
+        <v>0.99698004827959796</v>
       </c>
       <c r="AA86" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y86,$V$51))</f>
-        <v>0.77887390322665384</v>
+        <f t="shared" si="14"/>
+        <v>0.98852055864309485</v>
       </c>
       <c r="AB86" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y86,$V$52))</f>
-        <v>0.39010982776012937</v>
+        <f t="shared" si="15"/>
+        <v>0.94436293999111653</v>
       </c>
     </row>
     <row r="87" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="160"/>
       <c r="C87" s="161" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D87" s="11">
         <v>1</v>
@@ -22574,17 +22103,31 @@
       <c r="I87" s="9"/>
       <c r="J87" s="136"/>
       <c r="M87" s="4"/>
-      <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
-      <c r="Z87" s="2"/>
-      <c r="AA87" s="2"/>
-      <c r="AB87" s="3"/>
+      <c r="X87" s="2">
+        <v>43</v>
+      </c>
+      <c r="Y87" s="2">
+        <f t="shared" si="12"/>
+        <v>43</v>
+      </c>
+      <c r="Z87" s="2">
+        <f t="shared" si="13"/>
+        <v>0.99736973200810464</v>
+      </c>
+      <c r="AA87" s="2">
+        <f t="shared" si="14"/>
+        <v>0.99124271410354214</v>
+      </c>
+      <c r="AB87" s="3">
+        <f t="shared" si="15"/>
+        <v>0.96121007434763417</v>
+      </c>
     </row>
     <row r="88" spans="1:28" ht="13" x14ac:dyDescent="0.2">
       <c r="A88" s="132"/>
       <c r="B88" s="138"/>
       <c r="C88" s="161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D88" s="11">
         <v>1</v>
@@ -22597,30 +22140,30 @@
       <c r="J88" s="136"/>
       <c r="M88" s="4"/>
       <c r="X88" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="Y88" s="2">
-        <f t="shared" ref="Y88:Y100" si="12">IF(X88&lt;$D$47,X88,$D$47)</f>
-        <v>33</v>
+        <f t="shared" si="12"/>
+        <v>44</v>
       </c>
       <c r="Z88" s="2">
-        <f t="shared" ref="Z88:Z100" si="13">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y88,$V$50))</f>
-        <v>0.95213699076773617</v>
+        <f t="shared" si="13"/>
+        <v>0.99770913234723224</v>
       </c>
       <c r="AA88" s="2">
-        <f t="shared" ref="AA88:AA100" si="14">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y88,$V$51))</f>
-        <v>0.80401006260267238</v>
+        <f t="shared" si="14"/>
+        <v>0.99338324245368448</v>
       </c>
       <c r="AB88" s="3">
-        <f t="shared" ref="AB88:AB100" si="15">$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y88,$V$52))</f>
-        <v>0.43826241244646302</v>
+        <f t="shared" si="15"/>
+        <v>0.9738901576488701</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="13" x14ac:dyDescent="0.2">
       <c r="A89" s="132"/>
       <c r="B89" s="138"/>
       <c r="C89" s="161" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D89" s="11">
         <v>1</v>
@@ -22633,30 +22176,30 @@
       <c r="J89" s="136"/>
       <c r="M89" s="4"/>
       <c r="X89" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Y89" s="2">
         <f t="shared" si="12"/>
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="Z89" s="2">
         <f t="shared" si="13"/>
-        <v>0.95634841677598337</v>
+        <v>0.99800473768503117</v>
       </c>
       <c r="AA89" s="2">
         <f t="shared" si="14"/>
-        <v>0.82726100700728289</v>
+        <v>0.99504892408153423</v>
       </c>
       <c r="AB89" s="3">
         <f t="shared" si="15"/>
-        <v>0.48806681063370827</v>
+        <v>0.98307494845487398</v>
       </c>
     </row>
     <row r="90" spans="1:28" ht="13" x14ac:dyDescent="0.2">
       <c r="A90" s="132"/>
       <c r="B90" s="138"/>
       <c r="C90" s="161" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D90" s="11">
         <v>2</v>
@@ -22669,30 +22212,30 @@
       <c r="J90" s="136"/>
       <c r="M90" s="4"/>
       <c r="X90" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Y90" s="2">
-        <f t="shared" si="12"/>
-        <v>35</v>
+        <f>IF(X90&lt;$D$47,X90,$D$47)</f>
+        <v>47</v>
       </c>
       <c r="Z90" s="2">
-        <f t="shared" si="13"/>
-        <v>0.96018928294465022</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y90,$V$50))</f>
+        <v>0.99848643875156384</v>
       </c>
       <c r="AA90" s="2">
-        <f t="shared" si="14"/>
-        <v>0.84861837111219418</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y90,$V$51))</f>
+        <v>0.99730874997545671</v>
       </c>
       <c r="AB90" s="3">
-        <f t="shared" si="15"/>
-        <v>0.5388311126886246</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y90,$V$52))</f>
+        <v>0.99371525106854153</v>
       </c>
     </row>
     <row r="91" spans="1:28" ht="13" x14ac:dyDescent="0.2">
       <c r="A91" s="132"/>
       <c r="B91" s="138"/>
       <c r="C91" s="161" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D91" s="11">
         <v>2</v>
@@ -22705,30 +22248,30 @@
       <c r="J91" s="136"/>
       <c r="M91" s="4"/>
       <c r="X91" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="Y91" s="2">
-        <f t="shared" si="12"/>
-        <v>36</v>
+        <f>IF(X91&lt;$D$47,X91,$D$47)</f>
+        <v>49</v>
       </c>
       <c r="Z91" s="2">
-        <f t="shared" si="13"/>
-        <v>0.96369219452298982</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y91,$V$50))</f>
+        <v>0.99885184637850311</v>
       </c>
       <c r="AA91" s="2">
-        <f t="shared" si="14"/>
-        <v>0.86809962595736223</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y91,$V$51))</f>
+        <v>0.99859473730011838</v>
       </c>
       <c r="AB91" s="3">
-        <f t="shared" si="15"/>
-        <v>0.58978033691130305</v>
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y91,$V$52))</f>
+        <v>0.99805805194152097</v>
       </c>
     </row>
     <row r="92" spans="1:28" ht="13" x14ac:dyDescent="0.2">
       <c r="A92" s="132"/>
       <c r="B92" s="138"/>
       <c r="C92" s="161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D92" s="11">
         <v>2</v>
@@ -22740,24 +22283,24 @@
       <c r="I92" s="9"/>
       <c r="J92" s="136"/>
       <c r="M92" s="4"/>
-      <c r="X92" s="2">
-        <v>37</v>
-      </c>
-      <c r="Y92" s="2">
-        <f t="shared" si="12"/>
-        <v>37</v>
-      </c>
-      <c r="Z92" s="2">
-        <f t="shared" si="13"/>
-        <v>0.96688688785174093</v>
-      </c>
-      <c r="AA92" s="2">
-        <f t="shared" si="14"/>
-        <v>0.88574549403919223</v>
-      </c>
-      <c r="AB92" s="3">
-        <f t="shared" si="15"/>
-        <v>0.6400860539065194</v>
+      <c r="X92" s="112">
+        <v>50</v>
+      </c>
+      <c r="Y92" s="114">
+        <f>IF(X92&lt;$D$47,X92,$D$47)</f>
+        <v>50</v>
+      </c>
+      <c r="Z92" s="112">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y92,$V$50))</f>
+        <v>0.999</v>
+      </c>
+      <c r="AA92" s="112">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y92,$V$51))</f>
+        <v>0.999</v>
+      </c>
+      <c r="AB92" s="114">
+        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y92,$V$52))</f>
+        <v>0.999</v>
       </c>
     </row>
     <row r="93" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -22772,25 +22315,6 @@
       <c r="J93" s="137"/>
       <c r="L93" s="70"/>
       <c r="M93" s="4"/>
-      <c r="X93" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y93" s="2">
-        <f t="shared" si="12"/>
-        <v>38</v>
-      </c>
-      <c r="Z93" s="2">
-        <f t="shared" si="13"/>
-        <v>0.96980048279597986</v>
-      </c>
-      <c r="AA93" s="2">
-        <f t="shared" si="14"/>
-        <v>0.90161701660824767</v>
-      </c>
-      <c r="AB93" s="3">
-        <f t="shared" si="15"/>
-        <v>0.68890364347565436</v>
-      </c>
     </row>
     <row r="94" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="134"/>
@@ -22806,59 +22330,21 @@
       <c r="J94" s="88"/>
       <c r="L94" s="70"/>
       <c r="M94" s="4"/>
-      <c r="X94" s="2">
-        <v>39</v>
-      </c>
-      <c r="Y94" s="2">
-        <f t="shared" si="12"/>
-        <v>39</v>
-      </c>
-      <c r="Z94" s="2">
-        <f t="shared" si="13"/>
-        <v>0.97245771296661832</v>
-      </c>
-      <c r="AA94" s="2">
-        <f t="shared" si="14"/>
-        <v>0.91579239067798501</v>
-      </c>
-      <c r="AB94" s="3">
-        <f t="shared" si="15"/>
-        <v>0.7354150565882891</v>
-      </c>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B95" s="119"/>
-      <c r="C95" s="267" t="s">
-        <v>86</v>
+      <c r="C95" s="237" t="s">
+        <v>82</v>
       </c>
       <c r="D95" s="156"/>
       <c r="E95" s="165"/>
-      <c r="F95" s="269"/>
+      <c r="F95" s="239"/>
       <c r="G95" s="171"/>
-      <c r="H95" s="268"/>
+      <c r="H95" s="238"/>
       <c r="I95" s="8"/>
       <c r="J95" s="120"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4"/>
-      <c r="X95" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y95" s="2">
-        <f t="shared" si="12"/>
-        <v>40</v>
-      </c>
-      <c r="Z95" s="2">
-        <f t="shared" si="13"/>
-        <v>0.9748811356849042</v>
-      </c>
-      <c r="AA95" s="2">
-        <f t="shared" si="14"/>
-        <v>0.92836369192022972</v>
-      </c>
-      <c r="AB95" s="3">
-        <f t="shared" si="15"/>
-        <v>0.77887390322665351</v>
-      </c>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B96" s="119"/>
@@ -22874,34 +22360,15 @@
       <c r="J96" s="120"/>
       <c r="L96" s="1"/>
       <c r="M96" s="4"/>
-      <c r="X96" s="2">
-        <v>41</v>
-      </c>
-      <c r="Y96" s="2">
-        <f t="shared" si="12"/>
-        <v>41</v>
-      </c>
-      <c r="Z96" s="2">
-        <f t="shared" si="13"/>
-        <v>0.9770913234723223</v>
-      </c>
-      <c r="AA96" s="2">
-        <f t="shared" si="14"/>
-        <v>0.93943359356008671</v>
-      </c>
-      <c r="AB96" s="3">
-        <f t="shared" si="15"/>
-        <v>0.81864885013023359</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="132"/>
       <c r="B97" s="119"/>
       <c r="C97" s="48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D97" s="118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E97" s="165"/>
       <c r="F97" s="118"/>
@@ -22910,27 +22377,8 @@
       <c r="I97" s="9"/>
       <c r="J97" s="120"/>
       <c r="M97" s="4"/>
-      <c r="X97" s="2">
-        <v>42</v>
-      </c>
-      <c r="Y97" s="2">
-        <f t="shared" si="12"/>
-        <v>42</v>
-      </c>
-      <c r="Z97" s="2">
-        <f t="shared" si="13"/>
-        <v>0.97910703869145954</v>
-      </c>
-      <c r="AA97" s="2">
-        <f t="shared" si="14"/>
-        <v>0.94911218123412744</v>
-      </c>
-      <c r="AB97" s="3">
-        <f t="shared" si="15"/>
-        <v>0.854260889277211</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="132"/>
       <c r="B98" s="119"/>
       <c r="C98" s="48" t="str">
@@ -22945,27 +22393,8 @@
       <c r="I98" s="9"/>
       <c r="J98" s="88"/>
       <c r="M98" s="4"/>
-      <c r="X98" s="2">
-        <v>43</v>
-      </c>
-      <c r="Y98" s="2">
-        <f t="shared" si="12"/>
-        <v>43</v>
-      </c>
-      <c r="Z98" s="2">
-        <f t="shared" si="13"/>
-        <v>0.98094539282036752</v>
-      </c>
-      <c r="AA98" s="2">
-        <f t="shared" si="14"/>
-        <v>0.9575139503645862</v>
-      </c>
-      <c r="AB98" s="3">
-        <f t="shared" si="15"/>
-        <v>0.88541019911038366</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B99" s="129"/>
       <c r="C99" s="48" t="str">
         <f>IF(D97="Average height and age","Stand age (yr)","")</f>
@@ -22979,63 +22408,25 @@
       <c r="I99" s="9"/>
       <c r="J99" s="88"/>
       <c r="M99" s="4"/>
-      <c r="X99" s="2">
-        <v>44</v>
-      </c>
-      <c r="Y99" s="2">
-        <f t="shared" si="12"/>
-        <v>44</v>
-      </c>
-      <c r="Z99" s="2">
-        <f t="shared" si="13"/>
-        <v>0.98262199171250619</v>
-      </c>
-      <c r="AA99" s="2">
-        <f t="shared" si="14"/>
-        <v>0.96475505686229612</v>
-      </c>
-      <c r="AB99" s="3">
-        <f t="shared" si="15"/>
-        <v>0.91198915992692475</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B100" s="129"/>
       <c r="C100" s="48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D100" s="198"/>
       <c r="E100" s="165"/>
-      <c r="F100" s="280"/>
+      <c r="F100" s="118"/>
       <c r="G100" s="171"/>
-      <c r="H100" s="280"/>
+      <c r="H100" s="118"/>
       <c r="I100" s="9"/>
       <c r="J100" s="88"/>
       <c r="M100" s="4"/>
-      <c r="X100" s="2">
-        <v>45</v>
-      </c>
-      <c r="Y100" s="2">
-        <f t="shared" si="12"/>
-        <v>45</v>
-      </c>
-      <c r="Z100" s="2">
-        <f t="shared" si="13"/>
-        <v>0.98415106807538888</v>
-      </c>
-      <c r="AA100" s="2">
-        <f t="shared" si="14"/>
-        <v>0.97095087488040932</v>
-      </c>
-      <c r="AB100" s="3">
-        <f t="shared" si="15"/>
-        <v>0.93407957479769954</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B101" s="119"/>
       <c r="C101" s="48" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D101" s="11">
         <v>1</v>
@@ -23047,13 +22438,8 @@
       <c r="I101" s="9"/>
       <c r="J101" s="120"/>
       <c r="M101" s="4"/>
-      <c r="X101" s="2"/>
-      <c r="Y101" s="2"/>
-      <c r="Z101" s="2"/>
-      <c r="AA101" s="2"/>
-      <c r="AB101" s="3"/>
-    </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="132"/>
       <c r="B102" s="119"/>
       <c r="C102" s="48" t="str">
@@ -23068,30 +22454,11 @@
       <c r="I102" s="9"/>
       <c r="J102" s="120"/>
       <c r="M102" s="4"/>
-      <c r="X102" s="2">
-        <v>47</v>
-      </c>
-      <c r="Y102" s="2">
-        <f>IF(X102&lt;$D$47,X102,$D$47)</f>
-        <v>47</v>
-      </c>
-      <c r="Z102" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y102,$V$50))</f>
-        <v>0.98681743261443589</v>
-      </c>
-      <c r="AA102" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y102,$V$51))</f>
-        <v>0.98065200211710901</v>
-      </c>
-      <c r="AB102" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y102,$V$52))</f>
-        <v>0.96594413189444128</v>
-      </c>
-    </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B103" s="119"/>
       <c r="C103" s="102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D103" s="11">
         <v>1</v>
@@ -23103,27 +22470,8 @@
       <c r="I103" s="9"/>
       <c r="J103" s="120"/>
       <c r="M103" s="4"/>
-      <c r="X103" s="2">
-        <v>49</v>
-      </c>
-      <c r="Y103" s="2">
-        <f>IF(X103&lt;$D$47,X103,$D$47)</f>
-        <v>49</v>
-      </c>
-      <c r="Z103" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y103,$V$50))</f>
-        <v>0.9890352180385682</v>
-      </c>
-      <c r="AA103" s="2">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y103,$V$51))</f>
-        <v>0.98745400781789527</v>
-      </c>
-      <c r="AB103" s="3">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y103,$V$52))</f>
-        <v>0.98443466735417506</v>
-      </c>
-    </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="132"/>
       <c r="B104" s="119"/>
       <c r="C104" s="102" t="str">
@@ -23138,27 +22486,8 @@
       <c r="I104" s="9"/>
       <c r="J104" s="120"/>
       <c r="M104" s="4"/>
-      <c r="X104" s="112">
-        <v>50</v>
-      </c>
-      <c r="Y104" s="2">
-        <f>IF(X104&lt;$D$47,X104,$D$47)</f>
-        <v>50</v>
-      </c>
-      <c r="Z104" s="112">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$50))*POWER(Y104,$V$50))</f>
-        <v>0.99</v>
-      </c>
-      <c r="AA104" s="112">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$51))*POWER(Y104,$V$51))</f>
-        <v>0.99</v>
-      </c>
-      <c r="AB104" s="114">
-        <f>$V$47+($V$46-$V$47)*EXP(-(-LN(1-$V$49)/POWER($D$47,$V$52))*POWER(Y104,$V$52))</f>
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B105" s="119"/>
       <c r="C105" s="102" t="str">
         <f>IF($D$103=1, "Distance to wood panel mill (km)", "")</f>
@@ -23173,7 +22502,7 @@
       <c r="J105" s="120"/>
       <c r="M105" s="4"/>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B106" s="119"/>
       <c r="C106" s="102" t="str">
         <f>IF($D$103=1, "Distance to saw mill (km)", "")</f>
@@ -23188,7 +22517,7 @@
       <c r="J106" s="120"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="132"/>
       <c r="B107" s="119"/>
       <c r="C107" s="102" t="str">
@@ -23206,7 +22535,7 @@
       <c r="J107" s="120"/>
       <c r="M107" s="4"/>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="132"/>
       <c r="B108" s="90"/>
       <c r="C108" s="102" t="str">
@@ -23222,42 +22551,42 @@
       <c r="J108" s="88"/>
       <c r="M108" s="4"/>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="132"/>
       <c r="B109" s="90"/>
       <c r="C109" s="102" t="str">
         <f>IF($D$103=1, "Efficiency of the biomass power plant", "")</f>
         <v>Efficiency of the biomass power plant</v>
       </c>
-      <c r="D109" s="275"/>
+      <c r="D109" s="154"/>
       <c r="E109" s="171"/>
-      <c r="F109" s="275"/>
+      <c r="F109" s="154"/>
       <c r="G109" s="171"/>
-      <c r="H109" s="275"/>
+      <c r="H109" s="154"/>
       <c r="I109" s="9"/>
       <c r="J109" s="88"/>
       <c r="M109" s="4"/>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="132"/>
       <c r="B110" s="91"/>
       <c r="C110" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D110" s="271"/>
-      <c r="E110" s="272"/>
-      <c r="F110" s="273"/>
+        <v>46</v>
+      </c>
+      <c r="D110" s="240"/>
+      <c r="E110" s="241"/>
+      <c r="F110" s="242"/>
       <c r="G110" s="185"/>
-      <c r="H110" s="273"/>
-      <c r="I110" s="274"/>
+      <c r="H110" s="242"/>
+      <c r="I110" s="243"/>
       <c r="J110" s="88"/>
       <c r="M110" s="4"/>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="132"/>
       <c r="B111" s="92"/>
       <c r="C111" s="127" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="165"/>
@@ -23268,10 +22597,10 @@
       <c r="J111" s="88"/>
       <c r="M111" s="4"/>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B112" s="92"/>
       <c r="C112" s="127" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="165"/>
@@ -23302,15 +22631,15 @@
     </row>
     <row r="114" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" s="91"/>
-      <c r="C114" s="276" t="s">
+      <c r="C114" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D114" s="277"/>
+      <c r="D114" s="245"/>
       <c r="E114" s="165"/>
-      <c r="F114" s="278"/>
+      <c r="F114" s="246"/>
       <c r="G114" s="171"/>
-      <c r="H114" s="278"/>
-      <c r="I114" s="279"/>
+      <c r="H114" s="246"/>
+      <c r="I114" s="247"/>
       <c r="J114" s="88"/>
       <c r="L114" s="39"/>
       <c r="M114" s="4"/>
@@ -23319,7 +22648,7 @@
     <row r="115" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B115" s="143"/>
       <c r="C115" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="165"/>
@@ -23335,7 +22664,7 @@
     <row r="116" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="143"/>
       <c r="C116" s="161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D116" s="115"/>
       <c r="E116" s="116"/>
@@ -23351,7 +22680,7 @@
     <row r="117" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B117" s="143"/>
       <c r="C117" s="161" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="103"/>
@@ -23365,7 +22694,7 @@
     <row r="118" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="143"/>
       <c r="C118" s="161" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="103"/>
@@ -23379,7 +22708,7 @@
     <row r="119" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B119" s="143"/>
       <c r="C119" s="161" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="103"/>
@@ -23393,7 +22722,7 @@
     <row r="120" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" s="143"/>
       <c r="C120" s="161" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="158"/>
@@ -23407,7 +22736,7 @@
     <row r="121" spans="2:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B121" s="143"/>
       <c r="C121" s="47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="196"/>
@@ -23421,7 +22750,7 @@
     <row r="122" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="143"/>
       <c r="C122" s="161" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D122" s="11">
         <v>2</v>
@@ -23438,7 +22767,7 @@
     <row r="123" spans="2:15" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" s="143"/>
       <c r="C123" s="161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D123" s="11">
         <v>2</v>
@@ -23455,7 +22784,7 @@
     <row r="124" spans="2:15" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="143"/>
       <c r="C124" s="161" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D124" s="11">
         <v>2</v>
@@ -23472,7 +22801,7 @@
     <row r="125" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="143"/>
       <c r="C125" s="161" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D125" s="11">
         <v>2</v>
@@ -23488,7 +22817,7 @@
     <row r="126" spans="2:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B126" s="143"/>
       <c r="C126" s="161" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D126" s="11">
         <v>2</v>
@@ -23504,7 +22833,7 @@
     <row r="127" spans="2:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" s="143"/>
       <c r="C127" s="161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D127" s="11">
         <v>2</v>
@@ -23545,14 +22874,14 @@
     </row>
     <row r="130" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="122"/>
-      <c r="C130" s="281" t="s">
-        <v>86</v>
+      <c r="C130" s="248" t="s">
+        <v>82</v>
       </c>
       <c r="D130" s="156"/>
       <c r="E130" s="165"/>
-      <c r="F130" s="268"/>
+      <c r="F130" s="238"/>
       <c r="G130" s="171"/>
-      <c r="H130" s="268"/>
+      <c r="H130" s="238"/>
       <c r="I130" s="8"/>
       <c r="J130" s="121"/>
       <c r="M130" s="4"/>
@@ -23574,10 +22903,10 @@
     <row r="132" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="122"/>
       <c r="C132" s="48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D132" s="118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E132" s="165"/>
       <c r="F132" s="118"/>
@@ -23620,11 +22949,11 @@
     <row r="135" spans="2:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B135" s="130"/>
       <c r="C135" s="48" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D135" s="198"/>
       <c r="E135" s="165"/>
-      <c r="F135" s="280"/>
+      <c r="F135" s="118"/>
       <c r="G135" s="171"/>
       <c r="H135" s="199"/>
       <c r="I135" s="9"/>
@@ -23634,7 +22963,7 @@
     <row r="136" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B136" s="122"/>
       <c r="C136" s="48" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D136" s="156">
         <v>1</v>
@@ -23665,7 +22994,7 @@
     <row r="138" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B138" s="122"/>
       <c r="C138" s="102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D138" s="11">
         <v>1</v>
@@ -23764,11 +23093,11 @@
         <f>IF($D$138=1, "Efficiency of the biomass power plant", "")</f>
         <v>Efficiency of the biomass power plant</v>
       </c>
-      <c r="D144" s="275"/>
+      <c r="D144" s="154"/>
       <c r="E144" s="171"/>
-      <c r="F144" s="275"/>
+      <c r="F144" s="154"/>
       <c r="G144" s="171"/>
-      <c r="H144" s="275"/>
+      <c r="H144" s="154"/>
       <c r="I144" s="9"/>
       <c r="J144" s="121"/>
       <c r="L144" s="1"/>
@@ -23777,21 +23106,21 @@
     <row r="145" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B145" s="99"/>
       <c r="C145" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D145" s="271"/>
-      <c r="E145" s="272"/>
-      <c r="F145" s="273"/>
+        <v>46</v>
+      </c>
+      <c r="D145" s="240"/>
+      <c r="E145" s="241"/>
+      <c r="F145" s="242"/>
       <c r="G145" s="185"/>
-      <c r="H145" s="273"/>
-      <c r="I145" s="274"/>
+      <c r="H145" s="242"/>
+      <c r="I145" s="243"/>
       <c r="J145" s="96"/>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B146" s="100"/>
       <c r="C146" s="127" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="165"/>
@@ -23805,7 +23134,7 @@
     <row r="147" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B147" s="100"/>
       <c r="C147" s="127" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="165"/>
@@ -23832,22 +23161,22 @@
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B149" s="99"/>
-      <c r="C149" s="276" t="s">
+      <c r="C149" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D149" s="277"/>
+      <c r="D149" s="245"/>
       <c r="E149" s="165"/>
-      <c r="F149" s="278"/>
+      <c r="F149" s="246"/>
       <c r="G149" s="171"/>
-      <c r="H149" s="278"/>
-      <c r="I149" s="279"/>
+      <c r="H149" s="246"/>
+      <c r="I149" s="247"/>
       <c r="J149" s="96"/>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B150" s="146"/>
       <c r="C150" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="165"/>
@@ -23861,7 +23190,7 @@
     <row r="151" spans="2:15" ht="25" x14ac:dyDescent="0.2">
       <c r="B151" s="146"/>
       <c r="C151" s="161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D151" s="115"/>
       <c r="E151" s="182"/>
@@ -23875,7 +23204,7 @@
     <row r="152" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B152" s="146"/>
       <c r="C152" s="161" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="103"/>
@@ -23889,7 +23218,7 @@
     <row r="153" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B153" s="146"/>
       <c r="C153" s="161" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="103"/>
@@ -23903,7 +23232,7 @@
     <row r="154" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B154" s="146"/>
       <c r="C154" s="161" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="103"/>
@@ -23917,7 +23246,7 @@
     <row r="155" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B155" s="146"/>
       <c r="C155" s="161" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="158"/>
@@ -23931,7 +23260,7 @@
     <row r="156" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B156" s="146"/>
       <c r="C156" s="47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="196"/>
@@ -23945,7 +23274,7 @@
     <row r="157" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B157" s="146"/>
       <c r="C157" s="161" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D157" s="11">
         <v>2</v>
@@ -23961,7 +23290,7 @@
     <row r="158" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B158" s="146"/>
       <c r="C158" s="161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D158" s="11">
         <v>2</v>
@@ -23977,7 +23306,7 @@
     <row r="159" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B159" s="146"/>
       <c r="C159" s="161" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D159" s="11">
         <v>2</v>
@@ -23993,7 +23322,7 @@
     <row r="160" spans="2:15" ht="13" x14ac:dyDescent="0.2">
       <c r="B160" s="146"/>
       <c r="C160" s="161" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D160" s="11">
         <v>2</v>
@@ -24011,7 +23340,7 @@
     <row r="161" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B161" s="146"/>
       <c r="C161" s="161" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D161" s="11">
         <v>2</v>
@@ -24029,7 +23358,7 @@
     <row r="162" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="146"/>
       <c r="C162" s="161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D162" s="11">
         <v>2</v>
@@ -24076,14 +23405,14 @@
     </row>
     <row r="165" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B165" s="119"/>
-      <c r="C165" s="267" t="s">
-        <v>86</v>
+      <c r="C165" s="237" t="s">
+        <v>82</v>
       </c>
       <c r="D165" s="156"/>
       <c r="E165" s="165"/>
-      <c r="F165" s="268"/>
+      <c r="F165" s="238"/>
       <c r="G165" s="171"/>
-      <c r="H165" s="269"/>
+      <c r="H165" s="239"/>
       <c r="I165" s="8"/>
       <c r="J165" s="120"/>
       <c r="M165" s="4"/>
@@ -24105,10 +23434,10 @@
     <row r="167" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B167" s="119"/>
       <c r="C167" s="48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D167" s="118" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E167" s="165"/>
       <c r="F167" s="118"/>
@@ -24151,11 +23480,11 @@
     <row r="170" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B170" s="129"/>
       <c r="C170" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="D170" s="280"/>
+        <v>83</v>
+      </c>
+      <c r="D170" s="118"/>
       <c r="E170" s="165"/>
-      <c r="F170" s="280"/>
+      <c r="F170" s="118"/>
       <c r="G170" s="171"/>
       <c r="H170" s="198"/>
       <c r="I170" s="9"/>
@@ -24166,7 +23495,7 @@
     <row r="171" spans="2:15" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B171" s="119"/>
       <c r="C171" s="48" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D171" s="156">
         <v>1</v>
@@ -24188,9 +23517,9 @@
       </c>
       <c r="D172" s="157"/>
       <c r="E172" s="169"/>
-      <c r="F172" s="270"/>
+      <c r="F172" s="10"/>
       <c r="G172" s="188"/>
-      <c r="H172" s="270"/>
+      <c r="H172" s="10"/>
       <c r="I172" s="9"/>
       <c r="J172" s="120"/>
       <c r="L172" s="70"/>
@@ -24199,7 +23528,7 @@
     <row r="173" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B173" s="119"/>
       <c r="C173" s="102" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D173" s="156">
         <v>1</v>
@@ -24295,11 +23624,11 @@
         <f>IF($D$173=1, "Efficiency of the biomass power plant", "")</f>
         <v>Efficiency of the biomass power plant</v>
       </c>
-      <c r="D179" s="275"/>
+      <c r="D179" s="154"/>
       <c r="E179" s="171"/>
-      <c r="F179" s="275"/>
+      <c r="F179" s="154"/>
       <c r="G179" s="171"/>
-      <c r="H179" s="275"/>
+      <c r="H179" s="154"/>
       <c r="I179" s="9"/>
       <c r="J179" s="88"/>
       <c r="M179" s="4"/>
@@ -24307,21 +23636,21 @@
     <row r="180" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B180" s="91"/>
       <c r="C180" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D180" s="271"/>
-      <c r="E180" s="272"/>
-      <c r="F180" s="273"/>
+        <v>46</v>
+      </c>
+      <c r="D180" s="240"/>
+      <c r="E180" s="241"/>
+      <c r="F180" s="242"/>
       <c r="G180" s="185"/>
-      <c r="H180" s="273"/>
-      <c r="I180" s="274"/>
+      <c r="H180" s="242"/>
+      <c r="I180" s="243"/>
       <c r="J180" s="88"/>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B181" s="92"/>
       <c r="C181" s="127" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="165"/>
@@ -24335,7 +23664,7 @@
     <row r="182" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="92"/>
       <c r="C182" s="127" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="165"/>
@@ -24362,15 +23691,15 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B184" s="91"/>
-      <c r="C184" s="276" t="s">
+      <c r="C184" s="244" t="s">
         <v>12</v>
       </c>
-      <c r="D184" s="277"/>
+      <c r="D184" s="245"/>
       <c r="E184" s="165"/>
-      <c r="F184" s="278"/>
+      <c r="F184" s="246"/>
       <c r="G184" s="171"/>
-      <c r="H184" s="278"/>
-      <c r="I184" s="279"/>
+      <c r="H184" s="246"/>
+      <c r="I184" s="247"/>
       <c r="J184" s="88"/>
       <c r="M184" s="4"/>
     </row>
@@ -24378,7 +23707,7 @@
       <c r="A185" s="132"/>
       <c r="B185" s="149"/>
       <c r="C185" s="47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D185" s="6"/>
       <c r="E185" s="165"/>
@@ -24393,7 +23722,7 @@
       <c r="A186" s="132"/>
       <c r="B186" s="149"/>
       <c r="C186" s="161" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D186" s="115"/>
       <c r="E186" s="182"/>
@@ -24406,9 +23735,9 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="132"/>
-      <c r="B187" s="257"/>
+      <c r="B187" s="149"/>
       <c r="C187" s="161" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D187" s="6"/>
       <c r="E187" s="103"/>
@@ -24421,9 +23750,9 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="132"/>
-      <c r="B188" s="257"/>
+      <c r="B188" s="149"/>
       <c r="C188" s="161" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="103"/>
@@ -24438,7 +23767,7 @@
       <c r="A189" s="132"/>
       <c r="B189" s="149"/>
       <c r="C189" s="161" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D189" s="6"/>
       <c r="E189" s="103"/>
@@ -24453,7 +23782,7 @@
     <row r="190" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="119"/>
       <c r="C190" s="161" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D190" s="7"/>
       <c r="E190" s="158"/>
@@ -24468,7 +23797,7 @@
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B191" s="119"/>
       <c r="C191" s="47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D191" s="7"/>
       <c r="E191" s="196"/>
@@ -24483,7 +23812,7 @@
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B192" s="119"/>
       <c r="C192" s="161" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D192" s="11">
         <v>2</v>
@@ -24500,7 +23829,7 @@
     <row r="193" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B193" s="119"/>
       <c r="C193" s="161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D193" s="11">
         <v>2</v>
@@ -24516,7 +23845,7 @@
     <row r="194" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B194" s="119"/>
       <c r="C194" s="161" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D194" s="11">
         <v>2</v>
@@ -24532,7 +23861,7 @@
     <row r="195" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B195" s="119"/>
       <c r="C195" s="161" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D195" s="11">
         <v>2</v>
@@ -24548,7 +23877,7 @@
     <row r="196" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B196" s="119"/>
       <c r="C196" s="161" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D196" s="11">
         <v>2</v>
@@ -24564,7 +23893,7 @@
     <row r="197" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B197" s="119"/>
       <c r="C197" s="161" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D197" s="11">
         <v>2</v>
@@ -24578,87 +23907,87 @@
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="2:15" ht="13" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="258"/>
-      <c r="C198" s="259"/>
-      <c r="D198" s="260"/>
-      <c r="E198" s="261"/>
-      <c r="F198" s="262"/>
-      <c r="G198" s="263"/>
-      <c r="H198" s="264"/>
-      <c r="I198" s="265"/>
-      <c r="J198" s="266"/>
+      <c r="B198" s="228"/>
+      <c r="C198" s="229"/>
+      <c r="D198" s="230"/>
+      <c r="E198" s="231"/>
+      <c r="F198" s="232"/>
+      <c r="G198" s="233"/>
+      <c r="H198" s="234"/>
+      <c r="I198" s="235"/>
+      <c r="J198" s="236"/>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B199" s="238"/>
-      <c r="C199" s="238"/>
-      <c r="D199" s="238"/>
-      <c r="E199" s="238"/>
-      <c r="F199" s="238"/>
-      <c r="G199" s="238"/>
-      <c r="H199" s="238"/>
-      <c r="I199" s="238"/>
-      <c r="J199" s="239"/>
+      <c r="B199" s="221"/>
+      <c r="C199" s="221"/>
+      <c r="D199" s="221"/>
+      <c r="E199" s="221"/>
+      <c r="F199" s="221"/>
+      <c r="G199" s="221"/>
+      <c r="H199" s="221"/>
+      <c r="I199" s="221"/>
+      <c r="J199" s="222"/>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B200" s="238"/>
-      <c r="C200" s="238"/>
-      <c r="D200" s="238"/>
-      <c r="E200" s="238"/>
-      <c r="F200" s="238"/>
-      <c r="G200" s="238"/>
-      <c r="H200" s="240"/>
-      <c r="I200" s="238"/>
-      <c r="J200" s="238"/>
+      <c r="B200" s="221"/>
+      <c r="C200" s="221"/>
+      <c r="D200" s="221"/>
+      <c r="E200" s="221"/>
+      <c r="F200" s="221"/>
+      <c r="G200" s="221"/>
+      <c r="H200" s="223"/>
+      <c r="I200" s="221"/>
+      <c r="J200" s="221"/>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="2:15" ht="13" x14ac:dyDescent="0.2">
-      <c r="B201" s="238"/>
-      <c r="C201" s="241"/>
-      <c r="D201" s="242"/>
-      <c r="E201" s="242"/>
-      <c r="F201" s="242"/>
-      <c r="G201" s="242"/>
-      <c r="H201" s="239"/>
-      <c r="I201" s="239"/>
-      <c r="J201" s="243"/>
+      <c r="B201" s="221"/>
+      <c r="C201" s="224"/>
+      <c r="D201" s="225"/>
+      <c r="E201" s="225"/>
+      <c r="F201" s="225"/>
+      <c r="G201" s="225"/>
+      <c r="H201" s="222"/>
+      <c r="I201" s="222"/>
+      <c r="J201" s="226"/>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B202" s="238"/>
-      <c r="C202" s="255"/>
-      <c r="D202" s="255"/>
-      <c r="E202" s="255"/>
-      <c r="F202" s="255"/>
-      <c r="G202" s="255"/>
-      <c r="H202" s="244"/>
-      <c r="I202" s="238"/>
-      <c r="J202" s="243"/>
+      <c r="B202" s="221"/>
+      <c r="C202" s="276"/>
+      <c r="D202" s="276"/>
+      <c r="E202" s="276"/>
+      <c r="F202" s="276"/>
+      <c r="G202" s="276"/>
+      <c r="H202" s="227"/>
+      <c r="I202" s="221"/>
+      <c r="J202" s="226"/>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B203" s="238"/>
-      <c r="C203" s="256"/>
-      <c r="D203" s="256"/>
-      <c r="E203" s="256"/>
-      <c r="F203" s="256"/>
-      <c r="G203" s="256"/>
-      <c r="H203" s="253"/>
-      <c r="I203" s="254"/>
-      <c r="J203" s="238"/>
+      <c r="B203" s="221"/>
+      <c r="C203" s="277"/>
+      <c r="D203" s="277"/>
+      <c r="E203" s="277"/>
+      <c r="F203" s="277"/>
+      <c r="G203" s="277"/>
+      <c r="H203" s="274"/>
+      <c r="I203" s="275"/>
+      <c r="J203" s="221"/>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B204" s="238"/>
-      <c r="C204" s="238"/>
-      <c r="D204" s="238"/>
-      <c r="E204" s="238"/>
-      <c r="F204" s="238"/>
-      <c r="G204" s="238"/>
-      <c r="H204" s="253"/>
-      <c r="I204" s="254"/>
-      <c r="J204" s="238"/>
+      <c r="B204" s="221"/>
+      <c r="C204" s="221"/>
+      <c r="D204" s="221"/>
+      <c r="E204" s="221"/>
+      <c r="F204" s="221"/>
+      <c r="G204" s="221"/>
+      <c r="H204" s="274"/>
+      <c r="I204" s="275"/>
+      <c r="J204" s="221"/>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="2:15" x14ac:dyDescent="0.2">
@@ -24805,33 +24134,33 @@
       <c r="M256" s="4"/>
     </row>
     <row r="257" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="238"/>
-      <c r="K257" s="238"/>
+      <c r="A257" s="221"/>
+      <c r="K257" s="221"/>
       <c r="M257" s="4"/>
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A258" s="238"/>
-      <c r="K258" s="238"/>
+      <c r="A258" s="221"/>
+      <c r="K258" s="221"/>
       <c r="M258" s="4"/>
     </row>
     <row r="259" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="238"/>
-      <c r="K259" s="238"/>
+      <c r="A259" s="221"/>
+      <c r="K259" s="221"/>
       <c r="M259" s="4"/>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A260" s="238"/>
-      <c r="K260" s="238"/>
+      <c r="A260" s="221"/>
+      <c r="K260" s="221"/>
       <c r="M260" s="4"/>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A261" s="238"/>
-      <c r="K261" s="238"/>
+      <c r="A261" s="221"/>
+      <c r="K261" s="221"/>
       <c r="M261" s="4"/>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A262" s="238"/>
-      <c r="K262" s="238"/>
+      <c r="A262" s="221"/>
+      <c r="K262" s="221"/>
       <c r="M262" s="4"/>
     </row>
     <row r="265" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -28994,394 +28323,390 @@
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.90625" style="235" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="235" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="235" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" style="235" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="235"/>
+    <col min="1" max="1" width="43.90625" style="219" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="219" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="219" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="219" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="219"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="233" t="s">
+    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A1" s="249" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="233" t="s">
+      <c r="B1" s="249" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="249" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="249" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="262" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A2" s="250" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="250"/>
+      <c r="C2" s="251"/>
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+    </row>
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="253" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="253" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="254">
+        <v>2880</v>
+      </c>
+      <c r="D3" s="254">
+        <v>2880</v>
+      </c>
+      <c r="E3" s="252" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="253" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="253" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="251">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="251">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="253" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="253" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="251">
+        <v>6</v>
+      </c>
+      <c r="D5" s="251">
+        <v>8</v>
+      </c>
+      <c r="E5" s="252" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="253" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="253" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="251">
+        <v>4</v>
+      </c>
+      <c r="D6" s="251">
+        <v>7</v>
+      </c>
+      <c r="E6" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="253" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="253" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="251">
+        <v>1</v>
+      </c>
+      <c r="D7" s="251">
+        <v>1</v>
+      </c>
+      <c r="E7" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="253" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="253" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="256">
+        <v>1.5200000000000001E-3</v>
+      </c>
+      <c r="D8" s="256">
+        <v>1.6559999999999999E-3</v>
+      </c>
+      <c r="E8" s="252" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="253" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="253" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="251">
+        <v>0.47</v>
+      </c>
+      <c r="D9" s="251">
+        <v>0.47</v>
+      </c>
+      <c r="E9" s="255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="253" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="253" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="233" t="s">
+      <c r="C10" s="251">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="251">
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="253" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="253" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="C11" s="257">
+        <v>1</v>
+      </c>
+      <c r="D11" s="257">
+        <v>1</v>
+      </c>
+      <c r="E11" s="255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="253" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="253" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="234" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="221" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="223"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="224" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="224" t="s">
+      <c r="C12" s="254">
+        <v>150</v>
+      </c>
+      <c r="D12" s="254">
+        <v>140</v>
+      </c>
+      <c r="E12" s="258" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="253" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="253" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="225">
-        <v>2880</v>
-      </c>
-      <c r="D3" s="225">
-        <v>2880</v>
-      </c>
-      <c r="E3" s="223" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="224" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="224" t="s">
+      <c r="C13" s="251">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D13" s="251">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E13" s="252" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A14" s="253" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="222">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="222">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="226" t="s">
+      <c r="B14" s="253" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="251">
+        <v>0</v>
+      </c>
+      <c r="D14" s="251">
+        <v>0</v>
+      </c>
+      <c r="E14" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="253" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="253" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="251">
+        <v>1</v>
+      </c>
+      <c r="D15" s="251">
+        <v>1</v>
+      </c>
+      <c r="E15" s="252" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="253" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="253" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="251">
+        <v>1</v>
+      </c>
+      <c r="D16" s="251">
+        <v>1</v>
+      </c>
+      <c r="E16" s="252" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="224" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="224" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="222">
-        <v>6</v>
-      </c>
-      <c r="D5" s="222">
+    <row r="17" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A17" s="259" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="259"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="260"/>
+      <c r="E17" s="255"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="253" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="253" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="257">
+        <v>3</v>
+      </c>
+      <c r="D18" s="257">
+        <v>3</v>
+      </c>
+      <c r="E18" s="255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+      <c r="A19" s="259" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="253" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="219" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="219">
+        <v>50</v>
+      </c>
+      <c r="D20" s="219">
+        <v>50</v>
+      </c>
+      <c r="E20" s="219" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="219" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="219" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="219">
+        <v>0</v>
+      </c>
+      <c r="D21" s="219">
+        <v>0</v>
+      </c>
+      <c r="E21" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="219" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="223" t="s">
+      <c r="B22" s="219" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="219">
+        <v>0</v>
+      </c>
+      <c r="D22" s="219">
+        <v>0</v>
+      </c>
+      <c r="E22" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="261" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="219" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="219">
+        <v>0</v>
+      </c>
+      <c r="D23" s="219">
+        <v>0</v>
+      </c>
+      <c r="E23" s="252" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="219" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="224" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="224" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="222">
-        <v>4</v>
-      </c>
-      <c r="D6" s="222">
-        <v>7</v>
-      </c>
-      <c r="E6" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="224" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="224" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="222">
-        <v>1</v>
-      </c>
-      <c r="D7" s="222">
-        <v>1</v>
-      </c>
-      <c r="E7" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="224" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="224" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="227">
-        <v>1.5200000000000001E-3</v>
-      </c>
-      <c r="D8" s="227">
-        <v>1.6559999999999999E-3</v>
-      </c>
-      <c r="E8" s="223" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="224" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="224" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="222">
-        <v>0.47</v>
-      </c>
-      <c r="D9" s="222">
-        <v>0.47</v>
-      </c>
-      <c r="E9" s="226" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="224" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="224" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="222">
-        <v>0.25</v>
-      </c>
-      <c r="D10" s="222">
-        <v>0.25</v>
-      </c>
-      <c r="E10" s="226" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="224" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="224" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="228">
-        <v>1</v>
-      </c>
-      <c r="D11" s="228">
-        <v>1</v>
-      </c>
-      <c r="E11" s="226" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="224" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="224" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="225">
-        <v>150</v>
-      </c>
-      <c r="D12" s="225">
-        <v>140</v>
-      </c>
-      <c r="E12" s="229" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="224" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="224" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="222">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="D13" s="222">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E13" s="223" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A14" s="224" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="224" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="222">
+      <c r="B24" s="219" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="219">
         <v>0</v>
       </c>
-      <c r="D14" s="222">
+      <c r="D24" s="219">
         <v>0</v>
       </c>
-      <c r="E14" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="224" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="224" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="222">
-        <v>1</v>
-      </c>
-      <c r="D15" s="222">
-        <v>1</v>
-      </c>
-      <c r="E15" s="223" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="224" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" s="224" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="222">
-        <v>1</v>
-      </c>
-      <c r="D16" s="222">
-        <v>1</v>
-      </c>
-      <c r="E16" s="223" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="230" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="230"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="226"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="224" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="224" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="228">
-        <v>3</v>
-      </c>
-      <c r="D18" s="228">
-        <v>3</v>
-      </c>
-      <c r="E18" s="226" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="230" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="236"/>
-      <c r="C19" s="236"/>
-      <c r="D19" s="236"/>
-      <c r="E19" s="236"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="224" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="236" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="236">
-        <v>50</v>
-      </c>
-      <c r="D20" s="236">
-        <v>50</v>
-      </c>
-      <c r="E20" s="236" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="236" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="236" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="236">
-        <v>0</v>
-      </c>
-      <c r="D21" s="236">
-        <v>0</v>
-      </c>
-      <c r="E21" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="236" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="236" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="236">
-        <v>0</v>
-      </c>
-      <c r="D22" s="236">
-        <v>0</v>
-      </c>
-      <c r="E22" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="232" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="236" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="236">
-        <v>0</v>
-      </c>
-      <c r="D23" s="236">
-        <v>0</v>
-      </c>
-      <c r="E23" s="223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="236" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="236" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="236">
-        <v>0</v>
-      </c>
-      <c r="D24" s="236">
-        <v>0</v>
-      </c>
-      <c r="E24" s="223" t="s">
+      <c r="E24" s="252" t="s">
         <v>21</v>
       </c>
     </row>
@@ -29400,39 +28725,39 @@
     <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F1" t="s">
-        <v>140</v>
+    <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="263" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="263" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="263" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="263" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="263" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="263" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <f>LN(2)/E2</f>
@@ -29447,13 +28772,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="0">LN(2)/E3</f>
@@ -29468,13 +28793,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -29489,13 +28814,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
@@ -29510,13 +28835,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
@@ -29531,13 +28856,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
@@ -29552,13 +28877,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
@@ -29573,13 +28898,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -29594,13 +28919,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" t="s">
-        <v>160</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
@@ -29620,85 +28945,85 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0AA443B-76B7-4ADE-AD54-F5907BC420A4}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="263" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="263" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="263" t="s">
         <v>161</v>
       </c>
-      <c r="B1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" t="s">
-        <v>167</v>
+      <c r="D1" s="263" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="263" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="263" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="263" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="263" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="237">
+        <v>100</v>
+      </c>
+      <c r="D2" s="220">
         <v>0.12550529999999999</v>
       </c>
-      <c r="E2" s="237">
+      <c r="E2" s="220">
         <v>7.9110609999999998E-2</v>
       </c>
-      <c r="F2" s="237">
+      <c r="F2" s="220">
         <v>-1.2173969999999999E-2</v>
       </c>
-      <c r="G2" s="237">
+      <c r="G2" s="220">
         <v>9.8886739999999996E-4</v>
       </c>
-      <c r="H2" s="237">
+      <c r="H2" s="220">
         <v>-2.749263E-5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="237">
+        <v>100</v>
+      </c>
+      <c r="D3" s="220">
         <v>-1.8501139999999999E-3</v>
       </c>
-      <c r="E3" s="237">
+      <c r="E3" s="220">
         <v>6.2660170000000001E-2</v>
       </c>
-      <c r="F3" s="237">
+      <c r="F3" s="220">
         <v>-5.5241619999999998E-4</v>
       </c>
-      <c r="G3" s="237">
+      <c r="G3" s="220">
         <v>2.6055509999999999E-5</v>
       </c>
       <c r="H3">
@@ -29707,196 +29032,113 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="237">
+        <v>100</v>
+      </c>
+      <c r="D4" s="220">
         <v>7.2214650000000005E-2</v>
       </c>
-      <c r="E4" s="237">
+      <c r="E4" s="220">
         <v>0.21171693999999999</v>
       </c>
-      <c r="F4" s="237">
+      <c r="F4" s="220">
         <v>0.26354071000000001</v>
       </c>
-      <c r="G4" s="237">
+      <c r="G4" s="220">
         <v>-9.9735950000000004E-2</v>
       </c>
-      <c r="H4" s="237">
+      <c r="H4" s="220">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="237">
+        <v>99</v>
+      </c>
+      <c r="D5" s="220">
         <v>0.1128803</v>
       </c>
-      <c r="E5" s="237">
+      <c r="E5" s="220">
         <v>0.13783139999999999</v>
       </c>
-      <c r="F5" s="237">
+      <c r="F5" s="220">
         <v>-2.4068889999999999E-2</v>
       </c>
-      <c r="G5" s="237">
+      <c r="G5" s="220">
         <v>6.55287009E-2</v>
       </c>
-      <c r="H5" s="237">
+      <c r="H5" s="220">
         <v>-7.7324819999999997E-5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="237">
+        <v>99</v>
+      </c>
+      <c r="D6" s="220">
         <v>6.55287009E-2</v>
       </c>
-      <c r="E6" s="237">
+      <c r="E6" s="220">
         <v>8.4521816E-2</v>
       </c>
-      <c r="F6" s="237">
+      <c r="F6" s="220">
         <v>9.7538376000000006E-3</v>
       </c>
-      <c r="G6" s="237">
+      <c r="G6" s="220">
         <v>-4.4453279999999998E-4</v>
       </c>
-      <c r="H6" s="237">
+      <c r="H6" s="220">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="237">
+        <v>99</v>
+      </c>
+      <c r="D7" s="220">
         <v>0.12530286199999999</v>
       </c>
-      <c r="E7" s="237">
+      <c r="E7" s="220">
         <v>0.38619093199999999</v>
       </c>
-      <c r="F7" s="237">
+      <c r="F7" s="220">
         <v>-7.2512729999999999E-3</v>
       </c>
-      <c r="G7" s="237">
+      <c r="G7" s="220">
         <v>1.3542422E-2</v>
       </c>
-      <c r="H7" s="237">
+      <c r="H7" s="220">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>176</v>
-      </c>
-    </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="237">
-        <f>D5+E5*$B$11+F5*POWER($B$11,2)+G5*POWER($B$11,3)</f>
-        <v>4.4729405175999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B13">
-        <f>D6+E6*$B$11+F6*POWER($B$11,2)+G6*POWER($B$11,3)</f>
-        <v>0.53122726730000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14">
-        <f>D7+E7*$B$13+F7*POWER($B$13,2)+G7*POWER($B$13,3)</f>
-        <v>0.33044188218535075</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>177</v>
-      </c>
+      <c r="B12" s="220"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="237">
-        <f>D2+E2*$B$11+F2*POWER($B$11,2)+G2*POWER($B$11,3)+H2*POWER($B$11,4)</f>
-        <v>0.30341362032000002</v>
-      </c>
-      <c r="C16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B17">
-        <f>D3+E3*$B$11+F3*POWER($B$11,2)+G3*POWER($B$11,3)+H3*POWER($B$11,4)</f>
-        <v>0.24161945943999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18">
-        <f>D4+E4*$B$17+F4*POWER($B$17,2)+G4*POWER($B$17,3)+H4*POWER($B$17,4)</f>
-        <v>0.13734823064813795</v>
-      </c>
+      <c r="B16" s="220"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
